--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -6,10 +6,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA-ICT-Dashboard-GitHub-AutoExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3F15DF8-12B4-4A95-AC9E-344BCFE47634}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C44F93B-9989-4597-9097-1F9C50380639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3416" uniqueCount="1057">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3417" uniqueCount="1058">
   <si>
     <t>TT</t>
   </si>
@@ -5014,6 +5014,9 @@
   <si>
     <t>10/7/2026 Đã cmt và gửi cho CNC
 10/8/2026 Đã ký C</t>
+  </si>
+  <si>
+    <t>test</t>
   </si>
 </sst>
 </file>
@@ -7451,6 +7454,180 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -7468,21 +7645,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7492,248 +7654,89 @@
     <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="61" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="43" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8396,92 +8399,92 @@
       <c r="AE3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="350" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="406" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="359" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="366" t="s">
+      <c r="D4" s="352" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="369" t="s">
+      <c r="E4" s="348" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="412" t="s">
+      <c r="F4" s="357" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="369" t="s">
+      <c r="G4" s="348" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="410" t="s">
+      <c r="H4" s="355" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="366" t="s">
+      <c r="I4" s="352" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="366" t="s">
+      <c r="J4" s="352" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="369" t="s">
+      <c r="K4" s="348" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="366" t="s">
+      <c r="L4" s="352" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="364" t="s">
+      <c r="M4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="365"/>
-      <c r="O4" s="364" t="s">
+      <c r="N4" s="364"/>
+      <c r="O4" s="363" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="365"/>
-      <c r="Q4" s="368" t="s">
+      <c r="P4" s="364"/>
+      <c r="Q4" s="362" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="365"/>
-      <c r="S4" s="364" t="s">
+      <c r="R4" s="364"/>
+      <c r="S4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="364"/>
-      <c r="U4" s="365"/>
-      <c r="V4" s="368" t="s">
+      <c r="T4" s="363"/>
+      <c r="U4" s="364"/>
+      <c r="V4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="W4" s="364"/>
-      <c r="X4" s="365"/>
-      <c r="Y4" s="371" t="s">
+      <c r="W4" s="363"/>
+      <c r="X4" s="364"/>
+      <c r="Y4" s="415" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="372"/>
-      <c r="AA4" s="359" t="s">
+      <c r="Z4" s="416"/>
+      <c r="AA4" s="412" t="s">
         <v>112</v>
       </c>
-      <c r="AB4" s="360"/>
-      <c r="AC4" s="360"/>
-      <c r="AD4" s="361"/>
-      <c r="AE4" s="369" t="s">
+      <c r="AB4" s="413"/>
+      <c r="AC4" s="413"/>
+      <c r="AD4" s="414"/>
+      <c r="AE4" s="348" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="367"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="413"/>
-      <c r="G5" s="370"/>
-      <c r="H5" s="411"/>
-      <c r="I5" s="367"/>
-      <c r="J5" s="367"/>
-      <c r="K5" s="370"/>
-      <c r="L5" s="367"/>
+      <c r="A5" s="351"/>
+      <c r="B5" s="407"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="353"/>
+      <c r="E5" s="354"/>
+      <c r="F5" s="358"/>
+      <c r="G5" s="354"/>
+      <c r="H5" s="356"/>
+      <c r="I5" s="353"/>
+      <c r="J5" s="353"/>
+      <c r="K5" s="354"/>
+      <c r="L5" s="353"/>
       <c r="M5" s="79" t="s">
         <v>52</v>
       </c>
@@ -8536,14 +8539,14 @@
       <c r="AD5" s="336" t="s">
         <v>118</v>
       </c>
-      <c r="AE5" s="416"/>
-      <c r="AG5" s="369" t="s">
+      <c r="AE5" s="361"/>
+      <c r="AG5" s="348" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="369" t="s">
+      <c r="AH5" s="348" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="369" t="s">
+      <c r="AI5" s="348" t="s">
         <v>121</v>
       </c>
     </row>
@@ -8579,9 +8582,9 @@
       <c r="AC6" s="86"/>
       <c r="AD6" s="86"/>
       <c r="AE6" s="74"/>
-      <c r="AG6" s="407"/>
-      <c r="AH6" s="407"/>
-      <c r="AI6" s="407"/>
+      <c r="AG6" s="349"/>
+      <c r="AH6" s="349"/>
+      <c r="AI6" s="349"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -22770,7 +22773,9 @@
       <c r="AB135" s="229"/>
       <c r="AC135" s="229"/>
       <c r="AD135" s="337"/>
-      <c r="AE135" s="92"/>
+      <c r="AE135" s="92" t="s">
+        <v>1057</v>
+      </c>
       <c r="AG135" s="238" t="str">
         <f t="shared" si="75"/>
         <v>LTIA-5.11-LTICT- 71110 -RFA-OTH-0012</v>
@@ -22882,29 +22887,29 @@
       <c r="C139" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D139" s="376" t="s">
+      <c r="D139" s="379" t="s">
         <v>21</v>
       </c>
-      <c r="E139" s="376"/>
-      <c r="F139" s="377"/>
+      <c r="E139" s="379"/>
+      <c r="F139" s="380"/>
       <c r="G139" s="46"/>
       <c r="H139" s="68"/>
-      <c r="I139" s="356" t="s">
+      <c r="I139" s="384" t="s">
         <v>14</v>
       </c>
-      <c r="J139" s="357"/>
-      <c r="K139" s="357"/>
-      <c r="L139" s="357"/>
-      <c r="M139" s="357"/>
-      <c r="N139" s="358"/>
-      <c r="O139" s="362" t="s">
+      <c r="J139" s="385"/>
+      <c r="K139" s="385"/>
+      <c r="L139" s="385"/>
+      <c r="M139" s="385"/>
+      <c r="N139" s="386"/>
+      <c r="O139" s="382" t="s">
         <v>7</v>
       </c>
-      <c r="P139" s="363"/>
-      <c r="Q139" s="362" t="s">
+      <c r="P139" s="383"/>
+      <c r="Q139" s="382" t="s">
         <v>109</v>
       </c>
-      <c r="R139" s="363"/>
+      <c r="R139" s="383"/>
       <c r="S139" s="1"/>
       <c r="T139" s="1"/>
       <c r="U139" s="140"/>
@@ -22926,19 +22931,19 @@
       <c r="C140" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="D140" s="354" t="s">
+      <c r="D140" s="404" t="s">
         <v>111</v>
       </c>
-      <c r="E140" s="354"/>
-      <c r="F140" s="355"/>
+      <c r="E140" s="404"/>
+      <c r="F140" s="405"/>
       <c r="G140" s="46"/>
       <c r="H140" s="46"/>
-      <c r="I140" s="356" t="s">
+      <c r="I140" s="384" t="s">
         <v>19</v>
       </c>
-      <c r="J140" s="357"/>
-      <c r="K140" s="357"/>
-      <c r="L140" s="358"/>
+      <c r="J140" s="385"/>
+      <c r="K140" s="385"/>
+      <c r="L140" s="386"/>
       <c r="M140" s="105">
         <f t="shared" ref="M140:M145" ca="1" si="84">N140/$N$140</f>
         <v>1</v>
@@ -22982,19 +22987,19 @@
       <c r="C141" s="167" t="s">
         <v>22</v>
       </c>
-      <c r="D141" s="354" t="s">
+      <c r="D141" s="404" t="s">
         <v>23</v>
       </c>
-      <c r="E141" s="354"/>
-      <c r="F141" s="355"/>
+      <c r="E141" s="404"/>
+      <c r="F141" s="405"/>
       <c r="G141" s="70"/>
       <c r="H141" s="6"/>
-      <c r="I141" s="379" t="s">
+      <c r="I141" s="387" t="s">
         <v>66</v>
       </c>
-      <c r="J141" s="380"/>
-      <c r="K141" s="380"/>
-      <c r="L141" s="381"/>
+      <c r="J141" s="388"/>
+      <c r="K141" s="388"/>
+      <c r="L141" s="389"/>
       <c r="M141" s="107">
         <f t="shared" ca="1" si="84"/>
         <v>0.5</v>
@@ -23040,18 +23045,18 @@
       <c r="C142" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="D142" s="354" t="s">
+      <c r="D142" s="404" t="s">
         <v>25</v>
       </c>
-      <c r="E142" s="354"/>
-      <c r="F142" s="355"/>
+      <c r="E142" s="404"/>
+      <c r="F142" s="405"/>
       <c r="H142" s="6"/>
-      <c r="I142" s="382" t="s">
+      <c r="I142" s="390" t="s">
         <v>67</v>
       </c>
-      <c r="J142" s="383"/>
-      <c r="K142" s="383"/>
-      <c r="L142" s="384"/>
+      <c r="J142" s="391"/>
+      <c r="K142" s="391"/>
+      <c r="L142" s="392"/>
       <c r="M142" s="109">
         <f t="shared" ca="1" si="84"/>
         <v>0.1044776119402985</v>
@@ -23097,19 +23102,19 @@
       <c r="C143" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="D143" s="354" t="s">
+      <c r="D143" s="404" t="s">
         <v>27</v>
       </c>
-      <c r="E143" s="354"/>
-      <c r="F143" s="355"/>
+      <c r="E143" s="404"/>
+      <c r="F143" s="405"/>
       <c r="G143" s="71"/>
       <c r="H143" s="6"/>
-      <c r="I143" s="385" t="s">
+      <c r="I143" s="393" t="s">
         <v>68</v>
       </c>
-      <c r="J143" s="386"/>
-      <c r="K143" s="386"/>
-      <c r="L143" s="387"/>
+      <c r="J143" s="394"/>
+      <c r="K143" s="394"/>
+      <c r="L143" s="395"/>
       <c r="M143" s="111">
         <f t="shared" ca="1" si="84"/>
         <v>0.20895522388059701</v>
@@ -23155,18 +23160,18 @@
       <c r="C144" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="D144" s="354" t="s">
+      <c r="D144" s="404" t="s">
         <v>29</v>
       </c>
-      <c r="E144" s="354"/>
-      <c r="F144" s="355"/>
+      <c r="E144" s="404"/>
+      <c r="F144" s="405"/>
       <c r="G144" s="72"/>
-      <c r="I144" s="388" t="s">
+      <c r="I144" s="396" t="s">
         <v>70</v>
       </c>
-      <c r="J144" s="389"/>
-      <c r="K144" s="389"/>
-      <c r="L144" s="390"/>
+      <c r="J144" s="397"/>
+      <c r="K144" s="397"/>
+      <c r="L144" s="398"/>
       <c r="M144" s="114">
         <f t="shared" ca="1" si="84"/>
         <v>7.4626865671641784E-2</v>
@@ -23214,18 +23219,18 @@
       <c r="C145" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="D145" s="354" t="s">
+      <c r="D145" s="404" t="s">
         <v>31</v>
       </c>
-      <c r="E145" s="354"/>
-      <c r="F145" s="355"/>
+      <c r="E145" s="404"/>
+      <c r="F145" s="405"/>
       <c r="H145" s="6"/>
-      <c r="I145" s="391" t="s">
+      <c r="I145" s="399" t="s">
         <v>71</v>
       </c>
-      <c r="J145" s="392"/>
-      <c r="K145" s="392"/>
-      <c r="L145" s="393"/>
+      <c r="J145" s="400"/>
+      <c r="K145" s="400"/>
+      <c r="L145" s="401"/>
       <c r="M145" s="113">
         <f t="shared" ca="1" si="84"/>
         <v>0.11194029850746269</v>
@@ -23245,11 +23250,11 @@
       <c r="C146" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="D146" s="354" t="s">
+      <c r="D146" s="404" t="s">
         <v>33</v>
       </c>
-      <c r="E146" s="354"/>
-      <c r="F146" s="355"/>
+      <c r="E146" s="404"/>
+      <c r="F146" s="405"/>
       <c r="H146" s="1" t="s">
         <v>11</v>
       </c>
@@ -23258,11 +23263,11 @@
       <c r="C147" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="D147" s="354" t="s">
+      <c r="D147" s="404" t="s">
         <v>35</v>
       </c>
-      <c r="E147" s="354"/>
-      <c r="F147" s="355"/>
+      <c r="E147" s="404"/>
+      <c r="F147" s="405"/>
       <c r="H147" s="13"/>
       <c r="I147" s="141"/>
       <c r="J147" s="141"/>
@@ -23290,14 +23295,14 @@
       <c r="AI147" s="1"/>
     </row>
     <row r="148" spans="1:35">
-      <c r="C148" s="394" t="s">
+      <c r="C148" s="402" t="s">
         <v>75</v>
       </c>
-      <c r="D148" s="350" t="s">
+      <c r="D148" s="408" t="s">
         <v>76</v>
       </c>
-      <c r="E148" s="350"/>
-      <c r="F148" s="351"/>
+      <c r="E148" s="408"/>
+      <c r="F148" s="409"/>
       <c r="H148" s="13"/>
       <c r="J148" s="141"/>
       <c r="K148" s="13"/>
@@ -23324,10 +23329,10 @@
       <c r="AI148" s="1"/>
     </row>
     <row r="149" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C149" s="395"/>
-      <c r="D149" s="352"/>
-      <c r="E149" s="352"/>
-      <c r="F149" s="353"/>
+      <c r="C149" s="403"/>
+      <c r="D149" s="410"/>
+      <c r="E149" s="410"/>
+      <c r="F149" s="411"/>
       <c r="H149" s="13"/>
       <c r="I149" s="141"/>
       <c r="J149" s="141"/>
@@ -23382,12 +23387,12 @@
       <c r="AI150" s="1"/>
     </row>
     <row r="151" spans="1:35">
-      <c r="C151" s="378" t="s">
+      <c r="C151" s="381" t="s">
         <v>41</v>
       </c>
-      <c r="D151" s="378"/>
-      <c r="E151" s="378"/>
-      <c r="F151" s="378"/>
+      <c r="D151" s="381"/>
+      <c r="E151" s="381"/>
+      <c r="F151" s="381"/>
       <c r="H151" s="13"/>
       <c r="I151" s="141"/>
       <c r="J151" s="141"/>
@@ -23418,11 +23423,11 @@
       <c r="C152" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D152" s="396" t="s">
+      <c r="D152" s="367" t="s">
         <v>91</v>
       </c>
-      <c r="E152" s="396"/>
-      <c r="F152" s="396"/>
+      <c r="E152" s="367"/>
+      <c r="F152" s="367"/>
       <c r="H152" s="13"/>
       <c r="I152" s="141"/>
       <c r="J152" s="141"/>
@@ -23453,11 +23458,11 @@
       <c r="C153" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D153" s="396" t="s">
+      <c r="D153" s="367" t="s">
         <v>92</v>
       </c>
-      <c r="E153" s="396"/>
-      <c r="F153" s="396"/>
+      <c r="E153" s="367"/>
+      <c r="F153" s="367"/>
       <c r="H153" s="13"/>
       <c r="I153" s="141"/>
       <c r="J153" s="141"/>
@@ -23488,11 +23493,11 @@
       <c r="C154" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D154" s="396" t="s">
+      <c r="D154" s="367" t="s">
         <v>93</v>
       </c>
-      <c r="E154" s="396"/>
-      <c r="F154" s="396"/>
+      <c r="E154" s="367"/>
+      <c r="F154" s="367"/>
       <c r="H154" s="13"/>
       <c r="I154" s="141"/>
       <c r="J154" s="141"/>
@@ -23547,12 +23552,12 @@
       <c r="AI155" s="1"/>
     </row>
     <row r="156" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C156" s="402" t="s">
+      <c r="C156" s="371" t="s">
         <v>96</v>
       </c>
-      <c r="D156" s="403"/>
-      <c r="E156" s="403"/>
-      <c r="F156" s="404"/>
+      <c r="D156" s="372"/>
+      <c r="E156" s="372"/>
+      <c r="F156" s="373"/>
       <c r="H156" s="13"/>
       <c r="I156" s="141"/>
       <c r="J156" s="141"/>
@@ -23583,11 +23588,11 @@
       <c r="C157" s="212" t="s">
         <v>81</v>
       </c>
-      <c r="D157" s="405" t="s">
+      <c r="D157" s="374" t="s">
         <v>97</v>
       </c>
-      <c r="E157" s="405"/>
-      <c r="F157" s="406"/>
+      <c r="E157" s="374"/>
+      <c r="F157" s="375"/>
       <c r="H157" s="13"/>
       <c r="I157" s="141"/>
       <c r="J157" s="141"/>
@@ -23618,101 +23623,101 @@
       <c r="C158" s="213" t="s">
         <v>82</v>
       </c>
-      <c r="D158" s="397" t="s">
+      <c r="D158" s="365" t="s">
         <v>98</v>
       </c>
-      <c r="E158" s="397"/>
-      <c r="F158" s="398"/>
+      <c r="E158" s="365"/>
+      <c r="F158" s="366"/>
     </row>
     <row r="159" spans="1:35">
       <c r="C159" s="213" t="s">
         <v>83</v>
       </c>
-      <c r="D159" s="397" t="s">
+      <c r="D159" s="365" t="s">
         <v>99</v>
       </c>
-      <c r="E159" s="397"/>
-      <c r="F159" s="398"/>
+      <c r="E159" s="365"/>
+      <c r="F159" s="366"/>
     </row>
     <row r="160" spans="1:35">
       <c r="C160" s="214" t="s">
         <v>84</v>
       </c>
-      <c r="D160" s="397" t="s">
+      <c r="D160" s="365" t="s">
         <v>100</v>
       </c>
-      <c r="E160" s="397"/>
-      <c r="F160" s="398"/>
+      <c r="E160" s="365"/>
+      <c r="F160" s="366"/>
     </row>
     <row r="161" spans="3:6">
       <c r="C161" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="D161" s="397" t="s">
+      <c r="D161" s="365" t="s">
         <v>101</v>
       </c>
-      <c r="E161" s="397"/>
-      <c r="F161" s="398"/>
+      <c r="E161" s="365"/>
+      <c r="F161" s="366"/>
     </row>
     <row r="162" spans="3:6" ht="18.75">
       <c r="C162" s="214" t="s">
         <v>86</v>
       </c>
-      <c r="D162" s="397" t="s">
+      <c r="D162" s="365" t="s">
         <v>102</v>
       </c>
-      <c r="E162" s="397"/>
-      <c r="F162" s="398"/>
+      <c r="E162" s="365"/>
+      <c r="F162" s="366"/>
     </row>
     <row r="163" spans="3:6" ht="18.75">
       <c r="C163" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="D163" s="397" t="s">
+      <c r="D163" s="365" t="s">
         <v>103</v>
       </c>
-      <c r="E163" s="397"/>
-      <c r="F163" s="398"/>
+      <c r="E163" s="365"/>
+      <c r="F163" s="366"/>
     </row>
     <row r="164" spans="3:6">
       <c r="C164" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="D164" s="399" t="s">
+      <c r="D164" s="368" t="s">
         <v>104</v>
       </c>
-      <c r="E164" s="400"/>
-      <c r="F164" s="401"/>
+      <c r="E164" s="369"/>
+      <c r="F164" s="370"/>
     </row>
     <row r="165" spans="3:6" ht="18.75">
       <c r="C165" s="215" t="s">
         <v>89</v>
       </c>
-      <c r="D165" s="397" t="s">
+      <c r="D165" s="365" t="s">
         <v>105</v>
       </c>
-      <c r="E165" s="397"/>
-      <c r="F165" s="398"/>
+      <c r="E165" s="365"/>
+      <c r="F165" s="366"/>
     </row>
     <row r="166" spans="3:6">
       <c r="C166" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="D166" s="397" t="s">
+      <c r="D166" s="365" t="s">
         <v>106</v>
       </c>
-      <c r="E166" s="397"/>
-      <c r="F166" s="398"/>
+      <c r="E166" s="365"/>
+      <c r="F166" s="366"/>
     </row>
     <row r="167" spans="3:6" ht="16.5" thickBot="1">
       <c r="C167" s="216" t="s">
         <v>94</v>
       </c>
-      <c r="D167" s="373" t="s">
+      <c r="D167" s="376" t="s">
         <v>107</v>
       </c>
-      <c r="E167" s="374"/>
-      <c r="F167" s="375"/>
+      <c r="E167" s="377"/>
+      <c r="F167" s="378"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:AE137" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
@@ -23721,6 +23726,49 @@
     </sortState>
   </autoFilter>
   <mergeCells count="59">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D148:F149"/>
+    <mergeCell ref="D140:F140"/>
+    <mergeCell ref="I140:L140"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="Q139:R139"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="D167:F167"/>
+    <mergeCell ref="D139:F139"/>
+    <mergeCell ref="C151:F151"/>
+    <mergeCell ref="O139:P139"/>
+    <mergeCell ref="I139:N139"/>
+    <mergeCell ref="I141:L141"/>
+    <mergeCell ref="I142:L142"/>
+    <mergeCell ref="I143:L143"/>
+    <mergeCell ref="I144:L144"/>
+    <mergeCell ref="I145:L145"/>
+    <mergeCell ref="C148:C149"/>
+    <mergeCell ref="D141:F141"/>
+    <mergeCell ref="D142:F142"/>
+    <mergeCell ref="D143:F143"/>
+    <mergeCell ref="D144:F144"/>
+    <mergeCell ref="D152:F152"/>
+    <mergeCell ref="D166:F166"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="D154:F154"/>
+    <mergeCell ref="D161:F161"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="C156:F156"/>
+    <mergeCell ref="D157:F157"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D160:F160"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -23737,49 +23785,6 @@
     <mergeCell ref="V4:X4"/>
     <mergeCell ref="M4:N4"/>
     <mergeCell ref="O4:P4"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="D161:F161"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="C156:F156"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="D167:F167"/>
-    <mergeCell ref="D139:F139"/>
-    <mergeCell ref="C151:F151"/>
-    <mergeCell ref="O139:P139"/>
-    <mergeCell ref="I139:N139"/>
-    <mergeCell ref="I141:L141"/>
-    <mergeCell ref="I142:L142"/>
-    <mergeCell ref="I143:L143"/>
-    <mergeCell ref="I144:L144"/>
-    <mergeCell ref="I145:L145"/>
-    <mergeCell ref="C148:C149"/>
-    <mergeCell ref="D141:F141"/>
-    <mergeCell ref="D142:F142"/>
-    <mergeCell ref="D143:F143"/>
-    <mergeCell ref="D144:F144"/>
-    <mergeCell ref="D152:F152"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D148:F149"/>
-    <mergeCell ref="D140:F140"/>
-    <mergeCell ref="I140:L140"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="Q139:R139"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="Y4:Z4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AE137 AG7:AI137">
@@ -24444,88 +24449,88 @@
       <c r="AD3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="350" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="406" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="359" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="369" t="s">
+      <c r="D4" s="348" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="412" t="s">
+      <c r="E4" s="357" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="369" t="s">
+      <c r="F4" s="348" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="410" t="s">
+      <c r="G4" s="355" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="366" t="s">
+      <c r="H4" s="352" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="366" t="s">
+      <c r="I4" s="352" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="369" t="s">
+      <c r="J4" s="348" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="366" t="s">
+      <c r="K4" s="352" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="364" t="s">
+      <c r="L4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="365"/>
-      <c r="N4" s="368" t="s">
+      <c r="M4" s="364"/>
+      <c r="N4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="365"/>
-      <c r="P4" s="368" t="s">
+      <c r="O4" s="364"/>
+      <c r="P4" s="362" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="365"/>
-      <c r="R4" s="364" t="s">
+      <c r="Q4" s="364"/>
+      <c r="R4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="364"/>
-      <c r="T4" s="365"/>
-      <c r="U4" s="368" t="s">
+      <c r="S4" s="363"/>
+      <c r="T4" s="364"/>
+      <c r="U4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="364"/>
-      <c r="W4" s="365"/>
-      <c r="X4" s="371" t="s">
+      <c r="V4" s="363"/>
+      <c r="W4" s="364"/>
+      <c r="X4" s="415" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="417"/>
-      <c r="Z4" s="371" t="s">
+      <c r="Y4" s="427"/>
+      <c r="Z4" s="415" t="s">
         <v>112</v>
       </c>
-      <c r="AA4" s="360"/>
-      <c r="AB4" s="360"/>
-      <c r="AC4" s="361"/>
-      <c r="AD4" s="369" t="s">
+      <c r="AA4" s="413"/>
+      <c r="AB4" s="413"/>
+      <c r="AC4" s="414"/>
+      <c r="AD4" s="348" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="370"/>
-      <c r="E5" s="413"/>
-      <c r="F5" s="370"/>
-      <c r="G5" s="411"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="367"/>
-      <c r="J5" s="370"/>
-      <c r="K5" s="367"/>
+      <c r="A5" s="351"/>
+      <c r="B5" s="407"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="354"/>
+      <c r="E5" s="358"/>
+      <c r="F5" s="354"/>
+      <c r="G5" s="356"/>
+      <c r="H5" s="353"/>
+      <c r="I5" s="353"/>
+      <c r="J5" s="354"/>
+      <c r="K5" s="353"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -24580,14 +24585,14 @@
       <c r="AC5" s="250" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="416"/>
-      <c r="AG5" s="422" t="s">
+      <c r="AD5" s="361"/>
+      <c r="AG5" s="417" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="424" t="s">
+      <c r="AH5" s="419" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="426" t="s">
+      <c r="AI5" s="421" t="s">
         <v>121</v>
       </c>
     </row>
@@ -24622,9 +24627,9 @@
       <c r="AB6" s="86"/>
       <c r="AC6" s="86"/>
       <c r="AD6" s="74"/>
-      <c r="AG6" s="423"/>
-      <c r="AH6" s="425"/>
-      <c r="AI6" s="427"/>
+      <c r="AG6" s="418"/>
+      <c r="AH6" s="420"/>
+      <c r="AI6" s="422"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -28312,28 +28317,28 @@
       <c r="C43" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="376" t="s">
+      <c r="D43" s="379" t="s">
         <v>21</v>
       </c>
-      <c r="E43" s="377"/>
+      <c r="E43" s="380"/>
       <c r="F43" s="46"/>
       <c r="G43" s="46"/>
-      <c r="H43" s="356" t="s">
+      <c r="H43" s="384" t="s">
         <v>14</v>
       </c>
-      <c r="I43" s="357"/>
-      <c r="J43" s="357"/>
-      <c r="K43" s="357"/>
-      <c r="L43" s="357"/>
-      <c r="M43" s="358"/>
-      <c r="N43" s="362" t="s">
+      <c r="I43" s="385"/>
+      <c r="J43" s="385"/>
+      <c r="K43" s="385"/>
+      <c r="L43" s="385"/>
+      <c r="M43" s="386"/>
+      <c r="N43" s="382" t="s">
         <v>7</v>
       </c>
-      <c r="O43" s="363"/>
-      <c r="P43" s="362" t="s">
+      <c r="O43" s="383"/>
+      <c r="P43" s="382" t="s">
         <v>109</v>
       </c>
-      <c r="Q43" s="363"/>
+      <c r="Q43" s="383"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
       <c r="T43" s="140"/>
@@ -28353,17 +28358,17 @@
       <c r="C44" s="195" t="s">
         <v>109</v>
       </c>
-      <c r="D44" s="420" t="s">
+      <c r="D44" s="425" t="s">
         <v>111</v>
       </c>
-      <c r="E44" s="421"/>
+      <c r="E44" s="426"/>
       <c r="F44" s="46"/>
-      <c r="H44" s="356" t="s">
+      <c r="H44" s="384" t="s">
         <v>18</v>
       </c>
-      <c r="I44" s="357"/>
-      <c r="J44" s="357"/>
-      <c r="K44" s="358"/>
+      <c r="I44" s="385"/>
+      <c r="J44" s="385"/>
+      <c r="K44" s="386"/>
       <c r="L44" s="105">
         <f ca="1">M44/$M$44</f>
         <v>1</v>
@@ -28405,18 +28410,18 @@
       <c r="C45" s="195" t="s">
         <v>36</v>
       </c>
-      <c r="D45" s="418" t="s">
+      <c r="D45" s="423" t="s">
         <v>37</v>
       </c>
-      <c r="E45" s="419"/>
+      <c r="E45" s="424"/>
       <c r="F45" s="69"/>
       <c r="G45" s="6"/>
-      <c r="H45" s="379" t="s">
+      <c r="H45" s="387" t="s">
         <v>66</v>
       </c>
-      <c r="I45" s="380"/>
-      <c r="J45" s="380"/>
-      <c r="K45" s="381"/>
+      <c r="I45" s="388"/>
+      <c r="J45" s="388"/>
+      <c r="K45" s="389"/>
       <c r="L45" s="107">
         <f ca="1">M45/$M$44</f>
         <v>2.7777777777777776E-2</v>
@@ -28457,21 +28462,21 @@
       <c r="AI45" s="11"/>
     </row>
     <row r="46" spans="1:35">
-      <c r="C46" s="394" t="s">
+      <c r="C46" s="402" t="s">
         <v>75</v>
       </c>
-      <c r="D46" s="350" t="s">
+      <c r="D46" s="408" t="s">
         <v>76</v>
       </c>
-      <c r="E46" s="351"/>
+      <c r="E46" s="409"/>
       <c r="F46" s="70"/>
       <c r="G46" s="6"/>
-      <c r="H46" s="382" t="s">
+      <c r="H46" s="390" t="s">
         <v>67</v>
       </c>
-      <c r="I46" s="383"/>
-      <c r="J46" s="383"/>
-      <c r="K46" s="384"/>
+      <c r="I46" s="391"/>
+      <c r="J46" s="391"/>
+      <c r="K46" s="392"/>
       <c r="L46" s="109">
         <f t="shared" ref="L46:L49" ca="1" si="21">M46/$M$44</f>
         <v>0.55555555555555558</v>
@@ -28512,17 +28517,17 @@
       <c r="AI46" s="11"/>
     </row>
     <row r="47" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C47" s="395"/>
-      <c r="D47" s="352"/>
-      <c r="E47" s="353"/>
+      <c r="C47" s="403"/>
+      <c r="D47" s="410"/>
+      <c r="E47" s="411"/>
       <c r="F47" s="71"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="385" t="s">
+      <c r="H47" s="393" t="s">
         <v>68</v>
       </c>
-      <c r="I47" s="386"/>
-      <c r="J47" s="386"/>
-      <c r="K47" s="387"/>
+      <c r="I47" s="394"/>
+      <c r="J47" s="394"/>
+      <c r="K47" s="395"/>
       <c r="L47" s="111">
         <f t="shared" ca="1" si="21"/>
         <v>0.22222222222222221</v>
@@ -28565,12 +28570,12 @@
     <row r="48" spans="1:35">
       <c r="F48" s="72"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="388" t="s">
+      <c r="H48" s="396" t="s">
         <v>70</v>
       </c>
-      <c r="I48" s="389"/>
-      <c r="J48" s="389"/>
-      <c r="K48" s="390"/>
+      <c r="I48" s="397"/>
+      <c r="J48" s="397"/>
+      <c r="K48" s="398"/>
       <c r="L48" s="114">
         <f t="shared" ca="1" si="21"/>
         <v>0.1388888888888889</v>
@@ -28613,17 +28618,17 @@
       <c r="AI48" s="11"/>
     </row>
     <row r="49" spans="3:17" ht="16.5" thickBot="1">
-      <c r="C49" s="378" t="s">
+      <c r="C49" s="381" t="s">
         <v>41</v>
       </c>
-      <c r="D49" s="378"/>
-      <c r="E49" s="378"/>
-      <c r="H49" s="391" t="s">
+      <c r="D49" s="381"/>
+      <c r="E49" s="381"/>
+      <c r="H49" s="399" t="s">
         <v>71</v>
       </c>
-      <c r="I49" s="392"/>
-      <c r="J49" s="392"/>
-      <c r="K49" s="393"/>
+      <c r="I49" s="400"/>
+      <c r="J49" s="400"/>
+      <c r="K49" s="401"/>
       <c r="L49" s="113">
         <f t="shared" ca="1" si="21"/>
         <v>5.5555555555555552E-2</v>
@@ -28668,6 +28673,27 @@
     </sortState>
   </autoFilter>
   <mergeCells count="37">
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="H47:K47"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:E47"/>
+    <mergeCell ref="D44:E44"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -28684,27 +28710,6 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="H47:K47"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:E47"/>
-    <mergeCell ref="D44:E44"/>
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="B4:B5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AD41 AG7:AI41">
@@ -28987,81 +28992,81 @@
       <c r="Z3" s="159"/>
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A4" s="348" t="s">
+      <c r="A4" s="406" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="348" t="s">
+      <c r="B4" s="406" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="414" t="s">
+      <c r="C4" s="359" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="369" t="s">
+      <c r="D4" s="348" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="437" t="s">
+      <c r="E4" s="428" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="369" t="s">
+      <c r="F4" s="348" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="439" t="s">
+      <c r="G4" s="430" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="366" t="s">
+      <c r="H4" s="352" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="441" t="s">
+      <c r="I4" s="432" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="369" t="s">
+      <c r="J4" s="348" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="366" t="s">
+      <c r="K4" s="352" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="368" t="s">
+      <c r="L4" s="362" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="365"/>
-      <c r="N4" s="368" t="s">
+      <c r="M4" s="364"/>
+      <c r="N4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="365"/>
-      <c r="P4" s="368" t="s">
+      <c r="O4" s="364"/>
+      <c r="P4" s="362" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="365"/>
-      <c r="R4" s="364" t="s">
+      <c r="Q4" s="364"/>
+      <c r="R4" s="363" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="364"/>
-      <c r="T4" s="365"/>
-      <c r="U4" s="368" t="s">
+      <c r="S4" s="363"/>
+      <c r="T4" s="364"/>
+      <c r="U4" s="362" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="364"/>
-      <c r="W4" s="364"/>
-      <c r="X4" s="371" t="s">
+      <c r="V4" s="363"/>
+      <c r="W4" s="363"/>
+      <c r="X4" s="415" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="372"/>
-      <c r="Z4" s="365" t="s">
+      <c r="Y4" s="416"/>
+      <c r="Z4" s="364" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="72" customHeight="1">
-      <c r="A5" s="349"/>
-      <c r="B5" s="349"/>
-      <c r="C5" s="415"/>
-      <c r="D5" s="370"/>
-      <c r="E5" s="438"/>
-      <c r="F5" s="370"/>
-      <c r="G5" s="440"/>
-      <c r="H5" s="367"/>
-      <c r="I5" s="442"/>
-      <c r="J5" s="370"/>
-      <c r="K5" s="367"/>
+      <c r="A5" s="407"/>
+      <c r="B5" s="407"/>
+      <c r="C5" s="360"/>
+      <c r="D5" s="354"/>
+      <c r="E5" s="429"/>
+      <c r="F5" s="354"/>
+      <c r="G5" s="431"/>
+      <c r="H5" s="353"/>
+      <c r="I5" s="433"/>
+      <c r="J5" s="354"/>
+      <c r="K5" s="353"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -29104,7 +29109,7 @@
       <c r="Y5" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="416"/>
+      <c r="Z5" s="361"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="78"/>
@@ -38167,28 +38172,28 @@
       <c r="C130" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="D130" s="428" t="s">
+      <c r="D130" s="441" t="s">
         <v>39</v>
       </c>
-      <c r="E130" s="429"/>
+      <c r="E130" s="442"/>
       <c r="F130" s="46"/>
       <c r="G130" s="68"/>
-      <c r="H130" s="356" t="s">
+      <c r="H130" s="384" t="s">
         <v>14</v>
       </c>
-      <c r="I130" s="357"/>
-      <c r="J130" s="357"/>
-      <c r="K130" s="357"/>
-      <c r="L130" s="357"/>
-      <c r="M130" s="358"/>
-      <c r="N130" s="362" t="s">
+      <c r="I130" s="385"/>
+      <c r="J130" s="385"/>
+      <c r="K130" s="385"/>
+      <c r="L130" s="385"/>
+      <c r="M130" s="386"/>
+      <c r="N130" s="382" t="s">
         <v>7</v>
       </c>
-      <c r="O130" s="363"/>
-      <c r="P130" s="362" t="s">
+      <c r="O130" s="383"/>
+      <c r="P130" s="382" t="s">
         <v>110</v>
       </c>
-      <c r="Q130" s="363"/>
+      <c r="Q130" s="383"/>
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
       <c r="T130" s="140"/>
@@ -38201,16 +38206,16 @@
       <c r="C131" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="D131" s="435" t="s">
+      <c r="D131" s="439" t="s">
         <v>77</v>
       </c>
-      <c r="E131" s="436"/>
+      <c r="E131" s="440"/>
       <c r="F131" s="46"/>
       <c r="G131" s="46"/>
-      <c r="H131" s="430" t="s">
+      <c r="H131" s="434" t="s">
         <v>17</v>
       </c>
-      <c r="I131" s="431"/>
+      <c r="I131" s="435"/>
       <c r="J131" s="130"/>
       <c r="K131" s="210"/>
       <c r="L131" s="117">
@@ -38244,21 +38249,21 @@
       <c r="Y131" s="11"/>
     </row>
     <row r="132" spans="3:25">
-      <c r="C132" s="394" t="s">
+      <c r="C132" s="402" t="s">
         <v>6</v>
       </c>
-      <c r="D132" s="435" t="s">
+      <c r="D132" s="439" t="s">
         <v>40</v>
       </c>
-      <c r="E132" s="436"/>
+      <c r="E132" s="440"/>
       <c r="F132" s="69"/>
       <c r="G132" s="6"/>
-      <c r="H132" s="432" t="s">
+      <c r="H132" s="436" t="s">
         <v>69</v>
       </c>
-      <c r="I132" s="433"/>
-      <c r="J132" s="433"/>
-      <c r="K132" s="434"/>
+      <c r="I132" s="437"/>
+      <c r="J132" s="437"/>
+      <c r="K132" s="438"/>
       <c r="L132" s="122">
         <f t="shared" ref="L132:L134" ca="1" si="58">M132/$M$131</f>
         <v>0.83064516129032262</v>
@@ -38292,17 +38297,17 @@
       <c r="Y132" s="11"/>
     </row>
     <row r="133" spans="3:25">
-      <c r="C133" s="394"/>
-      <c r="D133" s="435"/>
-      <c r="E133" s="436"/>
+      <c r="C133" s="402"/>
+      <c r="D133" s="439"/>
+      <c r="E133" s="440"/>
       <c r="F133" s="72"/>
       <c r="G133" s="6"/>
-      <c r="H133" s="388" t="s">
+      <c r="H133" s="396" t="s">
         <v>70</v>
       </c>
-      <c r="I133" s="389"/>
-      <c r="J133" s="389"/>
-      <c r="K133" s="390"/>
+      <c r="I133" s="397"/>
+      <c r="J133" s="397"/>
+      <c r="K133" s="398"/>
       <c r="L133" s="124">
         <f t="shared" ca="1" si="58"/>
         <v>5.6451612903225805E-2</v>
@@ -38338,19 +38343,19 @@
       <c r="Y133" s="11"/>
     </row>
     <row r="134" spans="3:25" ht="16.5" thickBot="1">
-      <c r="C134" s="394" t="s">
+      <c r="C134" s="402" t="s">
         <v>75</v>
       </c>
-      <c r="D134" s="350" t="s">
+      <c r="D134" s="408" t="s">
         <v>76</v>
       </c>
-      <c r="E134" s="351"/>
-      <c r="H134" s="391" t="s">
+      <c r="E134" s="409"/>
+      <c r="H134" s="399" t="s">
         <v>71</v>
       </c>
-      <c r="I134" s="392"/>
-      <c r="J134" s="392"/>
-      <c r="K134" s="393"/>
+      <c r="I134" s="400"/>
+      <c r="J134" s="400"/>
+      <c r="K134" s="401"/>
       <c r="L134" s="126">
         <f t="shared" ca="1" si="58"/>
         <v>0.11290322580645161</v>
@@ -38365,16 +38370,16 @@
       <c r="Q134" s="224"/>
     </row>
     <row r="135" spans="3:25" ht="16.5" thickBot="1">
-      <c r="C135" s="395"/>
-      <c r="D135" s="352"/>
-      <c r="E135" s="353"/>
+      <c r="C135" s="403"/>
+      <c r="D135" s="410"/>
+      <c r="E135" s="411"/>
     </row>
     <row r="137" spans="3:25">
-      <c r="C137" s="378" t="s">
+      <c r="C137" s="381" t="s">
         <v>41</v>
       </c>
-      <c r="D137" s="378"/>
-      <c r="E137" s="378"/>
+      <c r="D137" s="381"/>
+      <c r="E137" s="381"/>
     </row>
     <row r="138" spans="3:25">
       <c r="C138" s="169" t="s">
@@ -38407,6 +38412,22 @@
     </sortState>
   </autoFilter>
   <mergeCells count="32">
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="P130:Q130"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D130:E130"/>
+    <mergeCell ref="H130:M130"/>
+    <mergeCell ref="N130:O130"/>
+    <mergeCell ref="H131:I131"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="H132:K132"/>
+    <mergeCell ref="H133:K133"/>
+    <mergeCell ref="H134:K134"/>
+    <mergeCell ref="D131:E131"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="D132:E133"/>
+    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="D134:E135"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D4:D5"/>
@@ -38423,22 +38444,6 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="H131:I131"/>
-    <mergeCell ref="C137:E137"/>
-    <mergeCell ref="H132:K132"/>
-    <mergeCell ref="H133:K133"/>
-    <mergeCell ref="H134:K134"/>
-    <mergeCell ref="D131:E131"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="D132:E133"/>
-    <mergeCell ref="C134:C135"/>
-    <mergeCell ref="D134:E135"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="P130:Q130"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D130:E130"/>
-    <mergeCell ref="H130:M130"/>
-    <mergeCell ref="N130:O130"/>
   </mergeCells>
   <phoneticPr fontId="71"/>
   <conditionalFormatting sqref="A7:Z128">
@@ -39020,19 +39025,19 @@
       <c r="S3" s="281"/>
     </row>
     <row r="4" spans="1:25" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="350" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="366" t="s">
+      <c r="B4" s="352" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="366" t="s">
+      <c r="C4" s="352" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="366" t="s">
+      <c r="D4" s="352" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="369" t="s">
+      <c r="E4" s="348" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="449" t="s">
@@ -39061,12 +39066,12 @@
       <c r="S4" s="448"/>
     </row>
     <row r="5" spans="1:25" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="367"/>
-      <c r="C5" s="367"/>
-      <c r="D5" s="367"/>
-      <c r="E5" s="370"/>
-      <c r="F5" s="411"/>
+      <c r="A5" s="351"/>
+      <c r="B5" s="353"/>
+      <c r="C5" s="353"/>
+      <c r="D5" s="353"/>
+      <c r="E5" s="354"/>
+      <c r="F5" s="356"/>
       <c r="G5" s="283" t="s">
         <v>56</v>
       </c>
@@ -40460,16 +40465,16 @@
       <c r="R3" s="281"/>
     </row>
     <row r="4" spans="1:18" ht="16.5" thickBot="1">
-      <c r="A4" s="408" t="s">
+      <c r="A4" s="350" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="366" t="s">
+      <c r="B4" s="352" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="366" t="s">
+      <c r="C4" s="352" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="364" t="s">
+      <c r="D4" s="363" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="449" t="s">
@@ -40498,11 +40503,11 @@
       <c r="R4" s="448"/>
     </row>
     <row r="5" spans="1:18" ht="78.75">
-      <c r="A5" s="409"/>
-      <c r="B5" s="367"/>
-      <c r="C5" s="367"/>
-      <c r="D5" s="440"/>
-      <c r="E5" s="370"/>
+      <c r="A5" s="351"/>
+      <c r="B5" s="353"/>
+      <c r="C5" s="353"/>
+      <c r="D5" s="431"/>
+      <c r="E5" s="354"/>
       <c r="F5" s="283" t="s">
         <v>56</v>
       </c>

--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -9,7 +9,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA-ICT-Dashboard-GitHub-AutoExcel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C44F93B-9989-4597-9097-1F9C50380639}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{615F497D-0951-4A5C-AE49-0733057F2AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3417" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3416" uniqueCount="1057">
   <si>
     <t>TT</t>
   </si>
@@ -5014,9 +5014,6 @@
   <si>
     <t>10/7/2026 Đã cmt và gửi cho CNC
 10/8/2026 Đã ký C</t>
-  </si>
-  <si>
-    <t>test</t>
   </si>
 </sst>
 </file>
@@ -22773,9 +22770,7 @@
       <c r="AB135" s="229"/>
       <c r="AC135" s="229"/>
       <c r="AD135" s="337"/>
-      <c r="AE135" s="92" t="s">
-        <v>1057</v>
-      </c>
+      <c r="AE135" s="92"/>
       <c r="AG135" s="238" t="str">
         <f t="shared" si="75"/>
         <v>LTIA-5.11-LTICT- 71110 -RFA-OTH-0012</v>

--- a/ICT-RFA-RFI-lists-New.xlsx
+++ b/ICT-RFA-RFI-lists-New.xlsx
@@ -6,12 +6,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA-ICT-Dashboard-GitHub-AutoExcel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Project Airport\LTIA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{615F497D-0951-4A5C-AE49-0733057F2AE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C0C2DFB-B61C-4FFB-8BE7-78404970B7BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" tabRatio="506" activeTab="1" xr2:uid="{CCA8147E-0981-4321-B87F-440A52C0DA59}"/>
   </bookViews>
   <sheets>
     <sheet name="RFA" sheetId="1" r:id="rId1"/>
@@ -78,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3416" uniqueCount="1057">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3419" uniqueCount="1058">
   <si>
     <t>TT</t>
   </si>
@@ -4868,9 +4868,6 @@
     <t>9/30/2026 Đã ký C</t>
   </si>
   <si>
-    <t>9/29/2026 Đã ký C</t>
-  </si>
-  <si>
     <t>9/22/2026 Đã ký A</t>
   </si>
   <si>
@@ -5014,6 +5011,14 @@
   <si>
     <t>10/7/2026 Đã cmt và gửi cho CNC
 10/8/2026 Đã ký C</t>
+  </si>
+  <si>
+    <t>9/29/2026 Đã ký C
+10/8/2026 Update
+10/8/2026 Đã ký A</t>
+  </si>
+  <si>
+    <t>10/9/2026 Update</t>
   </si>
 </sst>
 </file>
@@ -7451,7 +7456,181 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7462,15 +7641,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -7492,170 +7662,20 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="52" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="51" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="52" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="18" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="55" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="56" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="60" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="49" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7675,20 +7695,32 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="36" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="58" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="58" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -7707,33 +7739,6 @@
     </xf>
     <xf numFmtId="0" fontId="56" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="45" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="48" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="57" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="8" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="53" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="47" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="45" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -8309,7 +8314,7 @@
       </c>
       <c r="J1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="K1" s="131"/>
       <c r="L1" s="197"/>
@@ -8396,92 +8401,92 @@
       <c r="AE3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="408" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="406" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="359" t="s">
+      <c r="C4" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="352" t="s">
+      <c r="D4" s="366" t="s">
         <v>95</v>
       </c>
-      <c r="E4" s="348" t="s">
+      <c r="E4" s="369" t="s">
         <v>46</v>
       </c>
-      <c r="F4" s="357" t="s">
+      <c r="F4" s="412" t="s">
         <v>47</v>
       </c>
-      <c r="G4" s="348" t="s">
+      <c r="G4" s="369" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="355" t="s">
+      <c r="H4" s="410" t="s">
         <v>5</v>
       </c>
-      <c r="I4" s="352" t="s">
+      <c r="I4" s="366" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="352" t="s">
+      <c r="J4" s="366" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="348" t="s">
+      <c r="K4" s="369" t="s">
         <v>78</v>
       </c>
-      <c r="L4" s="352" t="s">
+      <c r="L4" s="366" t="s">
         <v>80</v>
       </c>
-      <c r="M4" s="363" t="s">
+      <c r="M4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="N4" s="364"/>
-      <c r="O4" s="363" t="s">
+      <c r="N4" s="365"/>
+      <c r="O4" s="364" t="s">
         <v>55</v>
       </c>
-      <c r="P4" s="364"/>
-      <c r="Q4" s="362" t="s">
+      <c r="P4" s="365"/>
+      <c r="Q4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="R4" s="364"/>
-      <c r="S4" s="363" t="s">
+      <c r="R4" s="365"/>
+      <c r="S4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="T4" s="363"/>
-      <c r="U4" s="364"/>
-      <c r="V4" s="362" t="s">
+      <c r="T4" s="364"/>
+      <c r="U4" s="365"/>
+      <c r="V4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="W4" s="363"/>
-      <c r="X4" s="364"/>
-      <c r="Y4" s="415" t="s">
+      <c r="W4" s="364"/>
+      <c r="X4" s="365"/>
+      <c r="Y4" s="371" t="s">
         <v>72</v>
       </c>
-      <c r="Z4" s="416"/>
-      <c r="AA4" s="412" t="s">
+      <c r="Z4" s="372"/>
+      <c r="AA4" s="359" t="s">
         <v>112</v>
       </c>
-      <c r="AB4" s="413"/>
-      <c r="AC4" s="413"/>
-      <c r="AD4" s="414"/>
-      <c r="AE4" s="348" t="s">
+      <c r="AB4" s="360"/>
+      <c r="AC4" s="360"/>
+      <c r="AD4" s="361"/>
+      <c r="AE4" s="369" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="351"/>
-      <c r="B5" s="407"/>
-      <c r="C5" s="360"/>
-      <c r="D5" s="353"/>
-      <c r="E5" s="354"/>
-      <c r="F5" s="358"/>
-      <c r="G5" s="354"/>
-      <c r="H5" s="356"/>
-      <c r="I5" s="353"/>
-      <c r="J5" s="353"/>
-      <c r="K5" s="354"/>
-      <c r="L5" s="353"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="415"/>
+      <c r="D5" s="367"/>
+      <c r="E5" s="370"/>
+      <c r="F5" s="413"/>
+      <c r="G5" s="370"/>
+      <c r="H5" s="411"/>
+      <c r="I5" s="367"/>
+      <c r="J5" s="367"/>
+      <c r="K5" s="370"/>
+      <c r="L5" s="367"/>
       <c r="M5" s="79" t="s">
         <v>52</v>
       </c>
@@ -8536,14 +8541,14 @@
       <c r="AD5" s="336" t="s">
         <v>118</v>
       </c>
-      <c r="AE5" s="361"/>
-      <c r="AG5" s="348" t="s">
+      <c r="AE5" s="416"/>
+      <c r="AG5" s="369" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="348" t="s">
+      <c r="AH5" s="369" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="348" t="s">
+      <c r="AI5" s="369" t="s">
         <v>121</v>
       </c>
     </row>
@@ -8579,9 +8584,9 @@
       <c r="AC6" s="86"/>
       <c r="AD6" s="86"/>
       <c r="AE6" s="74"/>
-      <c r="AG6" s="349"/>
-      <c r="AH6" s="349"/>
-      <c r="AI6" s="349"/>
+      <c r="AG6" s="407"/>
+      <c r="AH6" s="407"/>
+      <c r="AI6" s="407"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -9500,7 +9505,7 @@
       </c>
       <c r="AD14" s="337">
         <f t="shared" ca="1" si="7"/>
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="AE14" s="92"/>
       <c r="AG14" s="238" t="str">
@@ -9616,7 +9621,7 @@
       </c>
       <c r="AD15" s="337">
         <f t="shared" ca="1" si="7"/>
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="AE15" s="92"/>
       <c r="AG15" s="238" t="str">
@@ -13004,7 +13009,7 @@
       </c>
       <c r="AD44" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="AE44" s="92"/>
       <c r="AG44" s="238" t="str">
@@ -13238,7 +13243,7 @@
       </c>
       <c r="AD46" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="AE46" s="92"/>
       <c r="AG46" s="238" t="str">
@@ -13704,7 +13709,7 @@
       </c>
       <c r="AD50" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AE50" s="92"/>
       <c r="AG50" s="238" t="str">
@@ -13755,7 +13760,7 @@
       <c r="I51" s="138"/>
       <c r="J51" s="164">
         <f t="shared" ca="1" si="3"/>
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="K51" s="47"/>
       <c r="L51" s="164" t="s">
@@ -14612,7 +14617,7 @@
       </c>
       <c r="AD58" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="AE58" s="92"/>
       <c r="AG58" s="238" t="str">
@@ -14663,7 +14668,7 @@
       <c r="I59" s="138"/>
       <c r="J59" s="164">
         <f t="shared" ca="1" si="3"/>
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="K59" s="47"/>
       <c r="L59" s="164" t="s">
@@ -14818,7 +14823,7 @@
       </c>
       <c r="AD60" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="AE60" s="92" t="s">
         <v>878</v>
@@ -14936,7 +14941,7 @@
       </c>
       <c r="AD61" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AE61" s="92"/>
       <c r="AG61" s="238" t="str">
@@ -15756,7 +15761,7 @@
       </c>
       <c r="AD68" s="337">
         <f t="shared" ca="1" si="13"/>
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AE68" s="92"/>
       <c r="AG68" s="238" t="str">
@@ -18378,11 +18383,11 @@
       <c r="I92" s="138"/>
       <c r="J92" s="164">
         <f t="shared" ca="1" si="27"/>
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K92" s="47">
         <f t="shared" ca="1" si="28"/>
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L92" s="164" t="s">
         <v>1004</v>
@@ -18480,11 +18485,11 @@
       </c>
       <c r="J93" s="164">
         <f t="shared" ca="1" si="27"/>
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K93" s="47">
         <f t="shared" ca="1" si="28"/>
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="L93" s="164" t="s">
         <v>13</v>
@@ -20219,7 +20224,7 @@
         <v/>
       </c>
       <c r="AE109" s="92" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="AG109" s="238" t="str">
         <f t="shared" si="14"/>
@@ -20376,11 +20381,11 @@
       <c r="I111" s="23"/>
       <c r="J111" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K111" s="47">
         <f t="shared" ca="1" si="31"/>
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L111" s="164" t="s">
         <v>13</v>
@@ -20739,7 +20744,7 @@
         <v/>
       </c>
       <c r="AE114" s="92" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="AG114" s="238" t="str">
         <f t="shared" si="14"/>
@@ -20847,7 +20852,7 @@
         <v/>
       </c>
       <c r="AE115" s="92" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="AG115" s="238" t="str">
         <f t="shared" si="14"/>
@@ -20959,7 +20964,7 @@
         <v/>
       </c>
       <c r="AE116" s="92" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="AG116" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21010,11 +21015,11 @@
       <c r="I117" s="138"/>
       <c r="J117" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K117" s="47">
         <f t="shared" ca="1" si="31"/>
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L117" s="164" t="s">
         <v>1004</v>
@@ -21253,7 +21258,7 @@
         <v/>
       </c>
       <c r="AE119" s="92" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="AG119" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21359,7 +21364,7 @@
         <v/>
       </c>
       <c r="AE120" s="92" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="AG120" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21689,7 +21694,7 @@
       </c>
       <c r="F124" s="174">
         <f t="shared" si="29"/>
-        <v>46301</v>
+        <v>46324</v>
       </c>
       <c r="G124" s="31" t="s">
         <v>983</v>
@@ -21698,14 +21703,14 @@
         <v>984</v>
       </c>
       <c r="I124" s="138" t="s">
+        <v>3</v>
+      </c>
+      <c r="J124" s="164">
+        <f t="shared" ca="1" si="30"/>
         <v>1</v>
       </c>
-      <c r="J124" s="164">
-        <f t="shared" si="30"/>
-        <v>20</v>
-      </c>
       <c r="K124" s="47">
-        <f t="shared" si="31"/>
+        <f t="shared" ca="1" si="31"/>
         <v>0</v>
       </c>
       <c r="L124" s="164"/>
@@ -21726,22 +21731,18 @@
         <v>46280</v>
       </c>
       <c r="U124" s="188">
-        <v>46280</v>
-      </c>
-      <c r="V124" s="29">
-        <v>46290</v>
-      </c>
-      <c r="W124" s="188">
-        <v>46300</v>
-      </c>
+        <v>46303</v>
+      </c>
+      <c r="V124" s="29"/>
+      <c r="W124" s="188"/>
       <c r="X124" s="235" t="s">
         <v>240</v>
       </c>
       <c r="Y124" s="230"/>
       <c r="Z124" s="227"/>
-      <c r="AA124" s="29">
+      <c r="AA124" s="29" t="b">
         <f t="shared" si="68"/>
-        <v>46307</v>
+        <v>0</v>
       </c>
       <c r="AB124" s="229"/>
       <c r="AC124" s="229" t="str">
@@ -21753,7 +21754,7 @@
         <v/>
       </c>
       <c r="AE124" s="92" t="s">
-        <v>1013</v>
+        <v>1056</v>
       </c>
       <c r="AG124" s="238" t="str">
         <f t="shared" si="14"/>
@@ -21772,7 +21773,7 @@
       </c>
       <c r="AI124" s="75" t="str">
         <f t="shared" ref="AI124:AI137" si="74">IF($AH124,IF(OR($R124="B",$R124="C"),"YES",IF($R124="",IF(OR($I124="B",$I124="C"),"YES",""),"")),"")</f>
-        <v>YES</v>
+        <v/>
       </c>
     </row>
     <row r="125" spans="1:35" s="9" customFormat="1" ht="47.25">
@@ -21859,7 +21860,7 @@
         <v/>
       </c>
       <c r="AE125" s="92" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="AG125" s="238" t="str">
         <f t="shared" ref="AG125:AG135" si="75">IF(AND(RIGHT($E125,1)&gt;="A",RIGHT($E125,1)&lt;="Z"),LEFT($E125,LEN($E125)-1),$E125)</f>
@@ -21965,7 +21966,7 @@
         <v/>
       </c>
       <c r="AE126" s="92" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="AG126" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22065,7 +22066,7 @@
       <c r="AC127" s="229"/>
       <c r="AD127" s="337"/>
       <c r="AE127" s="92" t="s">
-        <v>1032</v>
+        <v>1031</v>
       </c>
       <c r="AG127" s="238" t="str">
         <f t="shared" si="75"/>
@@ -22118,7 +22119,7 @@
       <c r="I128" s="138"/>
       <c r="J128" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K128" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22191,22 +22192,22 @@
         <v>32</v>
       </c>
       <c r="E129" s="25" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="F129" s="174">
         <f t="shared" si="29"/>
         <v>46319</v>
       </c>
       <c r="G129" s="31" t="s">
+        <v>1029</v>
+      </c>
+      <c r="H129" s="21" t="s">
         <v>1030</v>
-      </c>
-      <c r="H129" s="21" t="s">
-        <v>1031</v>
       </c>
       <c r="I129" s="138"/>
       <c r="J129" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K129" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22279,22 +22280,22 @@
         <v>32</v>
       </c>
       <c r="E130" s="25" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
       <c r="F130" s="174">
         <f t="shared" si="29"/>
         <v>46321</v>
       </c>
       <c r="G130" s="31" t="s">
+        <v>1034</v>
+      </c>
+      <c r="H130" s="21" t="s">
         <v>1035</v>
-      </c>
-      <c r="H130" s="21" t="s">
-        <v>1036</v>
       </c>
       <c r="I130" s="138"/>
       <c r="J130" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K130" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22367,22 +22368,22 @@
         <v>32</v>
       </c>
       <c r="E131" s="25" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="F131" s="174">
         <f t="shared" si="29"/>
         <v>46321</v>
       </c>
       <c r="G131" s="31" t="s">
+        <v>1038</v>
+      </c>
+      <c r="H131" s="21" t="s">
         <v>1039</v>
-      </c>
-      <c r="H131" s="21" t="s">
-        <v>1040</v>
       </c>
       <c r="I131" s="138"/>
       <c r="J131" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K131" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22455,22 +22456,22 @@
         <v>32</v>
       </c>
       <c r="E132" s="25" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="F132" s="174">
         <f t="shared" si="29"/>
         <v>46322</v>
       </c>
       <c r="G132" s="31" t="s">
+        <v>1041</v>
+      </c>
+      <c r="H132" s="21" t="s">
         <v>1042</v>
-      </c>
-      <c r="H132" s="21" t="s">
-        <v>1043</v>
       </c>
       <c r="I132" s="138"/>
       <c r="J132" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K132" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22543,22 +22544,22 @@
         <v>32</v>
       </c>
       <c r="E133" s="25" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="F133" s="174">
         <f t="shared" si="29"/>
         <v>46322</v>
       </c>
       <c r="G133" s="31" t="s">
+        <v>1044</v>
+      </c>
+      <c r="H133" s="21" t="s">
         <v>1045</v>
-      </c>
-      <c r="H133" s="21" t="s">
-        <v>1046</v>
       </c>
       <c r="I133" s="138"/>
       <c r="J133" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K133" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22631,22 +22632,22 @@
         <v>32</v>
       </c>
       <c r="E134" s="25" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="F134" s="174">
         <f t="shared" si="29"/>
         <v>46322</v>
       </c>
       <c r="G134" s="31" t="s">
+        <v>1047</v>
+      </c>
+      <c r="H134" s="21" t="s">
         <v>1048</v>
-      </c>
-      <c r="H134" s="21" t="s">
-        <v>1049</v>
       </c>
       <c r="I134" s="138"/>
       <c r="J134" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K134" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22719,22 +22720,22 @@
         <v>28</v>
       </c>
       <c r="E135" s="25" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="F135" s="174">
         <f t="shared" si="29"/>
         <v>46322</v>
       </c>
       <c r="G135" s="31" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H135" s="21" t="s">
         <v>1051</v>
-      </c>
-      <c r="H135" s="21" t="s">
-        <v>1052</v>
       </c>
       <c r="I135" s="138"/>
       <c r="J135" s="164">
         <f t="shared" ca="1" si="30"/>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K135" s="47">
         <f t="shared" ca="1" si="31"/>
@@ -22882,29 +22883,29 @@
       <c r="C139" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D139" s="379" t="s">
+      <c r="D139" s="376" t="s">
         <v>21</v>
       </c>
-      <c r="E139" s="379"/>
-      <c r="F139" s="380"/>
+      <c r="E139" s="376"/>
+      <c r="F139" s="377"/>
       <c r="G139" s="46"/>
       <c r="H139" s="68"/>
-      <c r="I139" s="384" t="s">
+      <c r="I139" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="J139" s="385"/>
-      <c r="K139" s="385"/>
-      <c r="L139" s="385"/>
-      <c r="M139" s="385"/>
-      <c r="N139" s="386"/>
-      <c r="O139" s="382" t="s">
+      <c r="J139" s="357"/>
+      <c r="K139" s="357"/>
+      <c r="L139" s="357"/>
+      <c r="M139" s="357"/>
+      <c r="N139" s="358"/>
+      <c r="O139" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="P139" s="383"/>
-      <c r="Q139" s="382" t="s">
+      <c r="P139" s="363"/>
+      <c r="Q139" s="362" t="s">
         <v>109</v>
       </c>
-      <c r="R139" s="383"/>
+      <c r="R139" s="363"/>
       <c r="S139" s="1"/>
       <c r="T139" s="1"/>
       <c r="U139" s="140"/>
@@ -22926,26 +22927,26 @@
       <c r="C140" s="167" t="s">
         <v>109</v>
       </c>
-      <c r="D140" s="404" t="s">
+      <c r="D140" s="354" t="s">
         <v>111</v>
       </c>
-      <c r="E140" s="404"/>
-      <c r="F140" s="405"/>
+      <c r="E140" s="354"/>
+      <c r="F140" s="355"/>
       <c r="G140" s="46"/>
       <c r="H140" s="46"/>
-      <c r="I140" s="384" t="s">
+      <c r="I140" s="356" t="s">
         <v>19</v>
       </c>
-      <c r="J140" s="385"/>
-      <c r="K140" s="385"/>
-      <c r="L140" s="386"/>
+      <c r="J140" s="357"/>
+      <c r="K140" s="357"/>
+      <c r="L140" s="358"/>
       <c r="M140" s="105">
         <f t="shared" ref="M140:M145" ca="1" si="84">N140/$N$140</f>
         <v>1</v>
       </c>
       <c r="N140" s="106">
         <f ca="1">SUM($N$141:$N$145)</f>
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="O140" s="102" t="s">
         <v>15</v>
@@ -22982,30 +22983,30 @@
       <c r="C141" s="167" t="s">
         <v>22</v>
       </c>
-      <c r="D141" s="404" t="s">
+      <c r="D141" s="354" t="s">
         <v>23</v>
       </c>
-      <c r="E141" s="404"/>
-      <c r="F141" s="405"/>
+      <c r="E141" s="354"/>
+      <c r="F141" s="355"/>
       <c r="G141" s="70"/>
       <c r="H141" s="6"/>
-      <c r="I141" s="387" t="s">
+      <c r="I141" s="379" t="s">
         <v>66</v>
       </c>
-      <c r="J141" s="388"/>
-      <c r="K141" s="388"/>
-      <c r="L141" s="389"/>
+      <c r="J141" s="380"/>
+      <c r="K141" s="380"/>
+      <c r="L141" s="381"/>
       <c r="M141" s="107">
         <f t="shared" ca="1" si="84"/>
-        <v>0.5</v>
+        <v>0.50370370370370365</v>
       </c>
       <c r="N141" s="108">
         <f>COUNTIF($I$7:$I$137,"A")</f>
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="O141" s="100">
         <f ca="1">COUNTIFS($J$7:$J$137,"&lt;=21",$I$7:$I$137,"A")</f>
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P141" s="101">
         <f ca="1">COUNTIFS($J$7:$J$137,"&gt;21",$I$7:$I$137,"A")</f>
@@ -23040,21 +23041,21 @@
       <c r="C142" s="167" t="s">
         <v>24</v>
       </c>
-      <c r="D142" s="404" t="s">
+      <c r="D142" s="354" t="s">
         <v>25</v>
       </c>
-      <c r="E142" s="404"/>
-      <c r="F142" s="405"/>
+      <c r="E142" s="354"/>
+      <c r="F142" s="355"/>
       <c r="H142" s="6"/>
-      <c r="I142" s="390" t="s">
+      <c r="I142" s="382" t="s">
         <v>67</v>
       </c>
-      <c r="J142" s="391"/>
-      <c r="K142" s="391"/>
-      <c r="L142" s="392"/>
+      <c r="J142" s="383"/>
+      <c r="K142" s="383"/>
+      <c r="L142" s="384"/>
       <c r="M142" s="109">
         <f t="shared" ca="1" si="84"/>
-        <v>0.1044776119402985</v>
+        <v>0.1037037037037037</v>
       </c>
       <c r="N142" s="110">
         <f>COUNTIF($I$7:$I$137,"B")</f>
@@ -23097,30 +23098,30 @@
       <c r="C143" s="167" t="s">
         <v>26</v>
       </c>
-      <c r="D143" s="404" t="s">
+      <c r="D143" s="354" t="s">
         <v>27</v>
       </c>
-      <c r="E143" s="404"/>
-      <c r="F143" s="405"/>
+      <c r="E143" s="354"/>
+      <c r="F143" s="355"/>
       <c r="G143" s="71"/>
       <c r="H143" s="6"/>
-      <c r="I143" s="393" t="s">
+      <c r="I143" s="385" t="s">
         <v>68</v>
       </c>
-      <c r="J143" s="394"/>
-      <c r="K143" s="394"/>
-      <c r="L143" s="395"/>
+      <c r="J143" s="386"/>
+      <c r="K143" s="386"/>
+      <c r="L143" s="387"/>
       <c r="M143" s="111">
         <f t="shared" ca="1" si="84"/>
-        <v>0.20895522388059701</v>
+        <v>0.2</v>
       </c>
       <c r="N143" s="112">
         <f>COUNTIF($I$7:$I$137,"C")</f>
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="O143" s="98">
         <f ca="1">COUNTIFS($J$7:$J$137,"&lt;=21",$I$7:$I$137,"C")</f>
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P143" s="50">
         <f ca="1">COUNTIFS($J$7:$J$137,"&gt;21",$I$7:$I$137,"C")</f>
@@ -23155,29 +23156,29 @@
       <c r="C144" s="168" t="s">
         <v>28</v>
       </c>
-      <c r="D144" s="404" t="s">
+      <c r="D144" s="354" t="s">
         <v>29</v>
       </c>
-      <c r="E144" s="404"/>
-      <c r="F144" s="405"/>
+      <c r="E144" s="354"/>
+      <c r="F144" s="355"/>
       <c r="G144" s="72"/>
-      <c r="I144" s="396" t="s">
+      <c r="I144" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="J144" s="397"/>
-      <c r="K144" s="397"/>
-      <c r="L144" s="398"/>
+      <c r="J144" s="389"/>
+      <c r="K144" s="389"/>
+      <c r="L144" s="390"/>
       <c r="M144" s="114">
         <f t="shared" ca="1" si="84"/>
-        <v>7.4626865671641784E-2</v>
+        <v>8.1481481481481488E-2</v>
       </c>
       <c r="N144" s="115">
         <f ca="1">SUM(O144:P144)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O144" s="98">
         <f ca="1">COUNTIFS($J$7:$J$137,"&lt;=21",$V$7:$V$137,"",$L$7:$L$137,"&lt;&gt;X")</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="P144" s="50">
         <f ca="1">COUNTIFS($J$7:$J$137,"&gt;21",$V$7:$V$137,"",$L$7:$L$137,"&lt;&gt;X")</f>
@@ -23214,21 +23215,21 @@
       <c r="C145" s="168" t="s">
         <v>30</v>
       </c>
-      <c r="D145" s="404" t="s">
+      <c r="D145" s="354" t="s">
         <v>31</v>
       </c>
-      <c r="E145" s="404"/>
-      <c r="F145" s="405"/>
+      <c r="E145" s="354"/>
+      <c r="F145" s="355"/>
       <c r="H145" s="6"/>
-      <c r="I145" s="399" t="s">
+      <c r="I145" s="391" t="s">
         <v>71</v>
       </c>
-      <c r="J145" s="400"/>
-      <c r="K145" s="400"/>
-      <c r="L145" s="401"/>
+      <c r="J145" s="392"/>
+      <c r="K145" s="392"/>
+      <c r="L145" s="393"/>
       <c r="M145" s="113">
         <f t="shared" ca="1" si="84"/>
-        <v>0.11194029850746269</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="N145" s="97">
         <f>COUNTIFS($L$7:$L$137,"X")</f>
@@ -23245,11 +23246,11 @@
       <c r="C146" s="168" t="s">
         <v>32</v>
       </c>
-      <c r="D146" s="404" t="s">
+      <c r="D146" s="354" t="s">
         <v>33</v>
       </c>
-      <c r="E146" s="404"/>
-      <c r="F146" s="405"/>
+      <c r="E146" s="354"/>
+      <c r="F146" s="355"/>
       <c r="H146" s="1" t="s">
         <v>11</v>
       </c>
@@ -23258,11 +23259,11 @@
       <c r="C147" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="D147" s="404" t="s">
+      <c r="D147" s="354" t="s">
         <v>35</v>
       </c>
-      <c r="E147" s="404"/>
-      <c r="F147" s="405"/>
+      <c r="E147" s="354"/>
+      <c r="F147" s="355"/>
       <c r="H147" s="13"/>
       <c r="I147" s="141"/>
       <c r="J147" s="141"/>
@@ -23290,14 +23291,14 @@
       <c r="AI147" s="1"/>
     </row>
     <row r="148" spans="1:35">
-      <c r="C148" s="402" t="s">
+      <c r="C148" s="394" t="s">
         <v>75</v>
       </c>
-      <c r="D148" s="408" t="s">
+      <c r="D148" s="350" t="s">
         <v>76</v>
       </c>
-      <c r="E148" s="408"/>
-      <c r="F148" s="409"/>
+      <c r="E148" s="350"/>
+      <c r="F148" s="351"/>
       <c r="H148" s="13"/>
       <c r="J148" s="141"/>
       <c r="K148" s="13"/>
@@ -23324,10 +23325,10 @@
       <c r="AI148" s="1"/>
     </row>
     <row r="149" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C149" s="403"/>
-      <c r="D149" s="410"/>
-      <c r="E149" s="410"/>
-      <c r="F149" s="411"/>
+      <c r="C149" s="395"/>
+      <c r="D149" s="352"/>
+      <c r="E149" s="352"/>
+      <c r="F149" s="353"/>
       <c r="H149" s="13"/>
       <c r="I149" s="141"/>
       <c r="J149" s="141"/>
@@ -23382,12 +23383,12 @@
       <c r="AI150" s="1"/>
     </row>
     <row r="151" spans="1:35">
-      <c r="C151" s="381" t="s">
+      <c r="C151" s="378" t="s">
         <v>41</v>
       </c>
-      <c r="D151" s="381"/>
-      <c r="E151" s="381"/>
-      <c r="F151" s="381"/>
+      <c r="D151" s="378"/>
+      <c r="E151" s="378"/>
+      <c r="F151" s="378"/>
       <c r="H151" s="13"/>
       <c r="I151" s="141"/>
       <c r="J151" s="141"/>
@@ -23418,11 +23419,11 @@
       <c r="C152" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D152" s="367" t="s">
+      <c r="D152" s="396" t="s">
         <v>91</v>
       </c>
-      <c r="E152" s="367"/>
-      <c r="F152" s="367"/>
+      <c r="E152" s="396"/>
+      <c r="F152" s="396"/>
       <c r="H152" s="13"/>
       <c r="I152" s="141"/>
       <c r="J152" s="141"/>
@@ -23453,11 +23454,11 @@
       <c r="C153" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D153" s="367" t="s">
+      <c r="D153" s="396" t="s">
         <v>92</v>
       </c>
-      <c r="E153" s="367"/>
-      <c r="F153" s="367"/>
+      <c r="E153" s="396"/>
+      <c r="F153" s="396"/>
       <c r="H153" s="13"/>
       <c r="I153" s="141"/>
       <c r="J153" s="141"/>
@@ -23488,11 +23489,11 @@
       <c r="C154" s="169" t="s">
         <v>8</v>
       </c>
-      <c r="D154" s="367" t="s">
+      <c r="D154" s="396" t="s">
         <v>93</v>
       </c>
-      <c r="E154" s="367"/>
-      <c r="F154" s="367"/>
+      <c r="E154" s="396"/>
+      <c r="F154" s="396"/>
       <c r="H154" s="13"/>
       <c r="I154" s="141"/>
       <c r="J154" s="141"/>
@@ -23547,12 +23548,12 @@
       <c r="AI155" s="1"/>
     </row>
     <row r="156" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C156" s="371" t="s">
+      <c r="C156" s="402" t="s">
         <v>96</v>
       </c>
-      <c r="D156" s="372"/>
-      <c r="E156" s="372"/>
-      <c r="F156" s="373"/>
+      <c r="D156" s="403"/>
+      <c r="E156" s="403"/>
+      <c r="F156" s="404"/>
       <c r="H156" s="13"/>
       <c r="I156" s="141"/>
       <c r="J156" s="141"/>
@@ -23583,11 +23584,11 @@
       <c r="C157" s="212" t="s">
         <v>81</v>
       </c>
-      <c r="D157" s="374" t="s">
+      <c r="D157" s="405" t="s">
         <v>97</v>
       </c>
-      <c r="E157" s="374"/>
-      <c r="F157" s="375"/>
+      <c r="E157" s="405"/>
+      <c r="F157" s="406"/>
       <c r="H157" s="13"/>
       <c r="I157" s="141"/>
       <c r="J157" s="141"/>
@@ -23618,101 +23619,101 @@
       <c r="C158" s="213" t="s">
         <v>82</v>
       </c>
-      <c r="D158" s="365" t="s">
+      <c r="D158" s="397" t="s">
         <v>98</v>
       </c>
-      <c r="E158" s="365"/>
-      <c r="F158" s="366"/>
+      <c r="E158" s="397"/>
+      <c r="F158" s="398"/>
     </row>
     <row r="159" spans="1:35">
       <c r="C159" s="213" t="s">
         <v>83</v>
       </c>
-      <c r="D159" s="365" t="s">
+      <c r="D159" s="397" t="s">
         <v>99</v>
       </c>
-      <c r="E159" s="365"/>
-      <c r="F159" s="366"/>
+      <c r="E159" s="397"/>
+      <c r="F159" s="398"/>
     </row>
     <row r="160" spans="1:35">
       <c r="C160" s="214" t="s">
         <v>84</v>
       </c>
-      <c r="D160" s="365" t="s">
+      <c r="D160" s="397" t="s">
         <v>100</v>
       </c>
-      <c r="E160" s="365"/>
-      <c r="F160" s="366"/>
+      <c r="E160" s="397"/>
+      <c r="F160" s="398"/>
     </row>
     <row r="161" spans="3:6">
       <c r="C161" s="214" t="s">
         <v>85</v>
       </c>
-      <c r="D161" s="365" t="s">
+      <c r="D161" s="397" t="s">
         <v>101</v>
       </c>
-      <c r="E161" s="365"/>
-      <c r="F161" s="366"/>
+      <c r="E161" s="397"/>
+      <c r="F161" s="398"/>
     </row>
     <row r="162" spans="3:6" ht="18.75">
       <c r="C162" s="214" t="s">
         <v>86</v>
       </c>
-      <c r="D162" s="365" t="s">
+      <c r="D162" s="397" t="s">
         <v>102</v>
       </c>
-      <c r="E162" s="365"/>
-      <c r="F162" s="366"/>
+      <c r="E162" s="397"/>
+      <c r="F162" s="398"/>
     </row>
     <row r="163" spans="3:6" ht="18.75">
       <c r="C163" s="213" t="s">
         <v>87</v>
       </c>
-      <c r="D163" s="365" t="s">
+      <c r="D163" s="397" t="s">
         <v>103</v>
       </c>
-      <c r="E163" s="365"/>
-      <c r="F163" s="366"/>
+      <c r="E163" s="397"/>
+      <c r="F163" s="398"/>
     </row>
     <row r="164" spans="3:6">
       <c r="C164" s="215" t="s">
         <v>88</v>
       </c>
-      <c r="D164" s="368" t="s">
+      <c r="D164" s="399" t="s">
         <v>104</v>
       </c>
-      <c r="E164" s="369"/>
-      <c r="F164" s="370"/>
+      <c r="E164" s="400"/>
+      <c r="F164" s="401"/>
     </row>
     <row r="165" spans="3:6" ht="18.75">
       <c r="C165" s="215" t="s">
         <v>89</v>
       </c>
-      <c r="D165" s="365" t="s">
+      <c r="D165" s="397" t="s">
         <v>105</v>
       </c>
-      <c r="E165" s="365"/>
-      <c r="F165" s="366"/>
+      <c r="E165" s="397"/>
+      <c r="F165" s="398"/>
     </row>
     <row r="166" spans="3:6">
       <c r="C166" s="213" t="s">
         <v>90</v>
       </c>
-      <c r="D166" s="365" t="s">
+      <c r="D166" s="397" t="s">
         <v>106</v>
       </c>
-      <c r="E166" s="365"/>
-      <c r="F166" s="366"/>
+      <c r="E166" s="397"/>
+      <c r="F166" s="398"/>
     </row>
     <row r="167" spans="3:6" ht="16.5" thickBot="1">
       <c r="C167" s="216" t="s">
         <v>94</v>
       </c>
-      <c r="D167" s="376" t="s">
+      <c r="D167" s="373" t="s">
         <v>107</v>
       </c>
-      <c r="E167" s="377"/>
-      <c r="F167" s="378"/>
+      <c r="E167" s="374"/>
+      <c r="F167" s="375"/>
     </row>
   </sheetData>
   <autoFilter ref="A6:AE137" xr:uid="{C724CDAB-378C-47DB-9F45-08EE3BFB6E8B}">
@@ -23721,20 +23722,35 @@
     </sortState>
   </autoFilter>
   <mergeCells count="59">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D148:F149"/>
-    <mergeCell ref="D140:F140"/>
-    <mergeCell ref="I140:L140"/>
-    <mergeCell ref="AA4:AD4"/>
-    <mergeCell ref="Q139:R139"/>
-    <mergeCell ref="D145:F145"/>
-    <mergeCell ref="D146:F146"/>
-    <mergeCell ref="D147:F147"/>
-    <mergeCell ref="S4:U4"/>
-    <mergeCell ref="L4:L5"/>
-    <mergeCell ref="Q4:R4"/>
-    <mergeCell ref="K4:K5"/>
-    <mergeCell ref="Y4:Z4"/>
+    <mergeCell ref="AG5:AG6"/>
+    <mergeCell ref="AH5:AH6"/>
+    <mergeCell ref="AI5:AI6"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="I4:I5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="H4:H5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="AE4:AE5"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="V4:X4"/>
+    <mergeCell ref="M4:N4"/>
+    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="D166:F166"/>
+    <mergeCell ref="D153:F153"/>
+    <mergeCell ref="D154:F154"/>
+    <mergeCell ref="D161:F161"/>
+    <mergeCell ref="D162:F162"/>
+    <mergeCell ref="D163:F163"/>
+    <mergeCell ref="D164:F164"/>
+    <mergeCell ref="D165:F165"/>
+    <mergeCell ref="C156:F156"/>
+    <mergeCell ref="D157:F157"/>
+    <mergeCell ref="D158:F158"/>
+    <mergeCell ref="D159:F159"/>
+    <mergeCell ref="D160:F160"/>
     <mergeCell ref="D167:F167"/>
     <mergeCell ref="D139:F139"/>
     <mergeCell ref="C151:F151"/>
@@ -23751,35 +23767,20 @@
     <mergeCell ref="D143:F143"/>
     <mergeCell ref="D144:F144"/>
     <mergeCell ref="D152:F152"/>
-    <mergeCell ref="D166:F166"/>
-    <mergeCell ref="D153:F153"/>
-    <mergeCell ref="D154:F154"/>
-    <mergeCell ref="D161:F161"/>
-    <mergeCell ref="D162:F162"/>
-    <mergeCell ref="D163:F163"/>
-    <mergeCell ref="D164:F164"/>
-    <mergeCell ref="D165:F165"/>
-    <mergeCell ref="C156:F156"/>
-    <mergeCell ref="D157:F157"/>
-    <mergeCell ref="D158:F158"/>
-    <mergeCell ref="D159:F159"/>
-    <mergeCell ref="D160:F160"/>
-    <mergeCell ref="AG5:AG6"/>
-    <mergeCell ref="AH5:AH6"/>
-    <mergeCell ref="AI5:AI6"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="I4:I5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="AE4:AE5"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="V4:X4"/>
-    <mergeCell ref="M4:N4"/>
-    <mergeCell ref="O4:P4"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="D148:F149"/>
+    <mergeCell ref="D140:F140"/>
+    <mergeCell ref="I140:L140"/>
+    <mergeCell ref="AA4:AD4"/>
+    <mergeCell ref="Q139:R139"/>
+    <mergeCell ref="D145:F145"/>
+    <mergeCell ref="D146:F146"/>
+    <mergeCell ref="D147:F147"/>
+    <mergeCell ref="S4:U4"/>
+    <mergeCell ref="L4:L5"/>
+    <mergeCell ref="Q4:R4"/>
+    <mergeCell ref="K4:K5"/>
+    <mergeCell ref="Y4:Z4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AE137 AG7:AI137">
@@ -24359,7 +24360,7 @@
       </c>
       <c r="I1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="197"/>
@@ -24444,88 +24445,88 @@
       <c r="AD3" s="159"/>
     </row>
     <row r="4" spans="1:35" s="5" customFormat="1" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="408" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="406" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="359" t="s">
+      <c r="C4" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="348" t="s">
+      <c r="D4" s="369" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="357" t="s">
+      <c r="E4" s="412" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="348" t="s">
+      <c r="F4" s="369" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="355" t="s">
+      <c r="G4" s="410" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="352" t="s">
+      <c r="H4" s="366" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="352" t="s">
+      <c r="I4" s="366" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="348" t="s">
+      <c r="J4" s="369" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="352" t="s">
+      <c r="K4" s="366" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="363" t="s">
+      <c r="L4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="364"/>
-      <c r="N4" s="362" t="s">
+      <c r="M4" s="365"/>
+      <c r="N4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="364"/>
-      <c r="P4" s="362" t="s">
+      <c r="O4" s="365"/>
+      <c r="P4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="364"/>
-      <c r="R4" s="363" t="s">
+      <c r="Q4" s="365"/>
+      <c r="R4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="363"/>
-      <c r="T4" s="364"/>
-      <c r="U4" s="362" t="s">
+      <c r="S4" s="364"/>
+      <c r="T4" s="365"/>
+      <c r="U4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="363"/>
-      <c r="W4" s="364"/>
-      <c r="X4" s="415" t="s">
+      <c r="V4" s="364"/>
+      <c r="W4" s="365"/>
+      <c r="X4" s="371" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="427"/>
-      <c r="Z4" s="415" t="s">
+      <c r="Y4" s="417"/>
+      <c r="Z4" s="371" t="s">
         <v>112</v>
       </c>
-      <c r="AA4" s="413"/>
-      <c r="AB4" s="413"/>
-      <c r="AC4" s="414"/>
-      <c r="AD4" s="348" t="s">
+      <c r="AA4" s="360"/>
+      <c r="AB4" s="360"/>
+      <c r="AC4" s="361"/>
+      <c r="AD4" s="369" t="s">
         <v>79</v>
       </c>
       <c r="AG4" s="236"/>
     </row>
     <row r="5" spans="1:35" ht="78.75">
-      <c r="A5" s="351"/>
-      <c r="B5" s="407"/>
-      <c r="C5" s="360"/>
-      <c r="D5" s="354"/>
-      <c r="E5" s="358"/>
-      <c r="F5" s="354"/>
-      <c r="G5" s="356"/>
-      <c r="H5" s="353"/>
-      <c r="I5" s="353"/>
-      <c r="J5" s="354"/>
-      <c r="K5" s="353"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="415"/>
+      <c r="D5" s="370"/>
+      <c r="E5" s="413"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="411"/>
+      <c r="H5" s="367"/>
+      <c r="I5" s="367"/>
+      <c r="J5" s="370"/>
+      <c r="K5" s="367"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -24580,14 +24581,14 @@
       <c r="AC5" s="250" t="s">
         <v>118</v>
       </c>
-      <c r="AD5" s="361"/>
-      <c r="AG5" s="417" t="s">
+      <c r="AD5" s="416"/>
+      <c r="AG5" s="422" t="s">
         <v>119</v>
       </c>
-      <c r="AH5" s="419" t="s">
+      <c r="AH5" s="424" t="s">
         <v>120</v>
       </c>
-      <c r="AI5" s="421" t="s">
+      <c r="AI5" s="426" t="s">
         <v>121</v>
       </c>
     </row>
@@ -24622,9 +24623,9 @@
       <c r="AB6" s="86"/>
       <c r="AC6" s="86"/>
       <c r="AD6" s="74"/>
-      <c r="AG6" s="418"/>
-      <c r="AH6" s="420"/>
-      <c r="AI6" s="422"/>
+      <c r="AG6" s="423"/>
+      <c r="AH6" s="425"/>
+      <c r="AI6" s="427"/>
     </row>
     <row r="7" spans="1:35" s="9" customFormat="1" ht="47.25">
       <c r="A7" s="33">
@@ -25300,7 +25301,7 @@
       </c>
       <c r="AC12" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="AD12" s="92"/>
       <c r="AG12" s="238" t="str">
@@ -25526,7 +25527,7 @@
       </c>
       <c r="AC14" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AD14" s="92"/>
       <c r="AG14" s="238" t="str">
@@ -25752,7 +25753,7 @@
       </c>
       <c r="AC16" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AD16" s="92"/>
       <c r="AG16" s="238" t="str">
@@ -25865,7 +25866,7 @@
       </c>
       <c r="AC17" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AD17" s="92"/>
       <c r="AG17" s="238" t="str">
@@ -25978,7 +25979,7 @@
       </c>
       <c r="AC18" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AD18" s="92"/>
       <c r="AG18" s="238" t="str">
@@ -26553,7 +26554,7 @@
       </c>
       <c r="AC23" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AD23" s="92"/>
       <c r="AG23" s="238" t="str">
@@ -26666,7 +26667,7 @@
       </c>
       <c r="AC24" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AD24" s="92"/>
       <c r="AG24" s="238" t="str">
@@ -26777,7 +26778,7 @@
       </c>
       <c r="AC25" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AD25" s="92" t="s">
         <v>887</v>
@@ -26892,7 +26893,7 @@
       </c>
       <c r="AC26" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AD26" s="92"/>
       <c r="AG26" s="238" t="str">
@@ -27005,7 +27006,7 @@
       </c>
       <c r="AC27" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AD27" s="92"/>
       <c r="AG27" s="238" t="str">
@@ -27324,7 +27325,7 @@
       </c>
       <c r="AC30" s="183">
         <f t="shared" ca="1" si="7"/>
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AD30" s="92" t="s">
         <v>593</v>
@@ -27379,11 +27380,11 @@
       </c>
       <c r="I31" s="164">
         <f ca="1">IF(ISBLANK($V31),_xlfn.DAYS($I$1,$T31),_xlfn.DAYS($V31,$T31))</f>
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J31" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K31" s="164"/>
       <c r="L31" s="54" t="s">
@@ -27771,7 +27772,7 @@
       </c>
       <c r="E35" s="174">
         <f t="shared" si="2"/>
-        <v>46289</v>
+        <v>46325</v>
       </c>
       <c r="F35" s="31" t="s">
         <v>977</v>
@@ -27782,11 +27783,11 @@
       <c r="H35" s="138"/>
       <c r="I35" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J35" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K35" s="164"/>
       <c r="L35" s="54" t="s">
@@ -27804,7 +27805,7 @@
         <v>46268</v>
       </c>
       <c r="T35" s="188">
-        <v>46268</v>
+        <v>46304</v>
       </c>
       <c r="U35" s="29"/>
       <c r="V35" s="188"/>
@@ -27824,7 +27825,9 @@
         <f t="shared" si="11"/>
         <v/>
       </c>
-      <c r="AD35" s="92"/>
+      <c r="AD35" s="92" t="s">
+        <v>1057</v>
+      </c>
       <c r="AG35" s="238" t="str">
         <f t="shared" si="8"/>
         <v>LTIA-5.10-VIETUR-80000-RFA-SDS-0417</v>
@@ -27976,11 +27979,11 @@
       </c>
       <c r="I37" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J37" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K37" s="164"/>
       <c r="L37" s="54" t="s">
@@ -28021,7 +28024,7 @@
         <v/>
       </c>
       <c r="AD37" s="92" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="AG37" s="238" t="str">
         <f t="shared" si="8"/>
@@ -28072,11 +28075,11 @@
         <v>1</v>
       </c>
       <c r="I38" s="164">
-        <f t="shared" ca="1" si="10"/>
-        <v>20</v>
+        <f t="shared" si="10"/>
+        <v>21</v>
       </c>
       <c r="J38" s="47">
-        <f t="shared" ca="1" si="4"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="K38" s="164"/>
@@ -28084,7 +28087,9 @@
         <v>8</v>
       </c>
       <c r="M38" s="65"/>
-      <c r="N38" s="40"/>
+      <c r="N38" s="40" t="s">
+        <v>8</v>
+      </c>
       <c r="O38" s="41"/>
       <c r="P38" s="40"/>
       <c r="Q38" s="155"/>
@@ -28097,16 +28102,20 @@
       <c r="T38" s="188">
         <v>46283</v>
       </c>
-      <c r="U38" s="29"/>
-      <c r="V38" s="188"/>
+      <c r="U38" s="29">
+        <v>46304</v>
+      </c>
+      <c r="V38" s="188">
+        <v>46304</v>
+      </c>
       <c r="W38" s="235" t="s">
         <v>240</v>
       </c>
       <c r="X38" s="230"/>
       <c r="Y38" s="227"/>
-      <c r="Z38" s="29" t="str">
+      <c r="Z38" s="29">
         <f t="shared" si="5"/>
-        <v/>
+        <v>46311</v>
       </c>
       <c r="AA38" s="229"/>
       <c r="AB38" s="229" t="str">
@@ -28118,7 +28127,7 @@
         <v/>
       </c>
       <c r="AD38" s="92" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="AG38" s="238" t="str">
         <f t="shared" si="8"/>
@@ -28157,7 +28166,7 @@
       </c>
       <c r="E39" s="174">
         <f t="shared" si="2"/>
-        <v>46289</v>
+        <v>46325</v>
       </c>
       <c r="F39" s="31" t="s">
         <v>994</v>
@@ -28168,11 +28177,11 @@
       <c r="H39" s="138"/>
       <c r="I39" s="164">
         <f t="shared" ca="1" si="10"/>
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="J39" s="47">
         <f t="shared" ca="1" si="4"/>
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K39" s="164"/>
       <c r="L39" s="54" t="s">
@@ -28190,7 +28199,7 @@
         <v>46268</v>
       </c>
       <c r="T39" s="188">
-        <v>46268</v>
+        <v>46304</v>
       </c>
       <c r="U39" s="29"/>
       <c r="V39" s="188"/>
@@ -28210,7 +28219,9 @@
         <f t="shared" ref="AC39" si="20">IF(AB39="Late Resubmission",IF(AA39="","",AA39-Z39),IF(AB39="Not submit yet",IF(Z39="","",$I$1-Z39),""))</f>
         <v/>
       </c>
-      <c r="AD39" s="92"/>
+      <c r="AD39" s="92" t="s">
+        <v>1057</v>
+      </c>
       <c r="AG39" s="238" t="str">
         <f t="shared" si="8"/>
         <v xml:space="preserve">  LTIA-5.10-VIETUR-80000-RFA-SDS-0394</v>
@@ -28312,28 +28323,28 @@
       <c r="C43" s="166" t="s">
         <v>20</v>
       </c>
-      <c r="D43" s="379" t="s">
+      <c r="D43" s="376" t="s">
         <v>21</v>
       </c>
-      <c r="E43" s="380"/>
+      <c r="E43" s="377"/>
       <c r="F43" s="46"/>
       <c r="G43" s="46"/>
-      <c r="H43" s="384" t="s">
+      <c r="H43" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="I43" s="385"/>
-      <c r="J43" s="385"/>
-      <c r="K43" s="385"/>
-      <c r="L43" s="385"/>
-      <c r="M43" s="386"/>
-      <c r="N43" s="382" t="s">
+      <c r="I43" s="357"/>
+      <c r="J43" s="357"/>
+      <c r="K43" s="357"/>
+      <c r="L43" s="357"/>
+      <c r="M43" s="358"/>
+      <c r="N43" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="O43" s="383"/>
-      <c r="P43" s="382" t="s">
+      <c r="O43" s="363"/>
+      <c r="P43" s="362" t="s">
         <v>109</v>
       </c>
-      <c r="Q43" s="383"/>
+      <c r="Q43" s="363"/>
       <c r="R43" s="1"/>
       <c r="S43" s="1"/>
       <c r="T43" s="140"/>
@@ -28353,24 +28364,24 @@
       <c r="C44" s="195" t="s">
         <v>109</v>
       </c>
-      <c r="D44" s="425" t="s">
+      <c r="D44" s="420" t="s">
         <v>111</v>
       </c>
-      <c r="E44" s="426"/>
+      <c r="E44" s="421"/>
       <c r="F44" s="46"/>
-      <c r="H44" s="384" t="s">
+      <c r="H44" s="356" t="s">
         <v>18</v>
       </c>
-      <c r="I44" s="385"/>
-      <c r="J44" s="385"/>
-      <c r="K44" s="386"/>
+      <c r="I44" s="357"/>
+      <c r="J44" s="357"/>
+      <c r="K44" s="358"/>
       <c r="L44" s="105">
         <f ca="1">M44/$M$44</f>
         <v>1</v>
       </c>
       <c r="M44" s="106">
         <f ca="1">SUM($M$45:$M$49)</f>
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N44" s="102" t="s">
         <v>15</v>
@@ -28405,21 +28416,21 @@
       <c r="C45" s="195" t="s">
         <v>36</v>
       </c>
-      <c r="D45" s="423" t="s">
+      <c r="D45" s="418" t="s">
         <v>37</v>
       </c>
-      <c r="E45" s="424"/>
+      <c r="E45" s="419"/>
       <c r="F45" s="69"/>
       <c r="G45" s="6"/>
-      <c r="H45" s="387" t="s">
+      <c r="H45" s="379" t="s">
         <v>66</v>
       </c>
-      <c r="I45" s="388"/>
-      <c r="J45" s="388"/>
-      <c r="K45" s="389"/>
+      <c r="I45" s="380"/>
+      <c r="J45" s="380"/>
+      <c r="K45" s="381"/>
       <c r="L45" s="107">
         <f ca="1">M45/$M$44</f>
-        <v>2.7777777777777776E-2</v>
+        <v>2.8571428571428571E-2</v>
       </c>
       <c r="M45" s="108">
         <f>COUNTIF($H$7:$H$41,"A")</f>
@@ -28457,24 +28468,24 @@
       <c r="AI45" s="11"/>
     </row>
     <row r="46" spans="1:35">
-      <c r="C46" s="402" t="s">
+      <c r="C46" s="394" t="s">
         <v>75</v>
       </c>
-      <c r="D46" s="408" t="s">
+      <c r="D46" s="350" t="s">
         <v>76</v>
       </c>
-      <c r="E46" s="409"/>
+      <c r="E46" s="351"/>
       <c r="F46" s="70"/>
       <c r="G46" s="6"/>
-      <c r="H46" s="390" t="s">
+      <c r="H46" s="382" t="s">
         <v>67</v>
       </c>
-      <c r="I46" s="391"/>
-      <c r="J46" s="391"/>
-      <c r="K46" s="392"/>
+      <c r="I46" s="383"/>
+      <c r="J46" s="383"/>
+      <c r="K46" s="384"/>
       <c r="L46" s="109">
         <f t="shared" ref="L46:L49" ca="1" si="21">M46/$M$44</f>
-        <v>0.55555555555555558</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="M46" s="110">
         <f>COUNTIF($H$7:$H$41,"B")</f>
@@ -28512,20 +28523,20 @@
       <c r="AI46" s="11"/>
     </row>
     <row r="47" spans="1:35" ht="16.5" thickBot="1">
-      <c r="C47" s="403"/>
-      <c r="D47" s="410"/>
-      <c r="E47" s="411"/>
+      <c r="C47" s="395"/>
+      <c r="D47" s="352"/>
+      <c r="E47" s="353"/>
       <c r="F47" s="71"/>
       <c r="G47" s="6"/>
-      <c r="H47" s="393" t="s">
+      <c r="H47" s="385" t="s">
         <v>68</v>
       </c>
-      <c r="I47" s="394"/>
-      <c r="J47" s="394"/>
-      <c r="K47" s="395"/>
+      <c r="I47" s="386"/>
+      <c r="J47" s="386"/>
+      <c r="K47" s="387"/>
       <c r="L47" s="111">
         <f t="shared" ca="1" si="21"/>
-        <v>0.22222222222222221</v>
+        <v>0.22857142857142856</v>
       </c>
       <c r="M47" s="112">
         <f>COUNTIF($H$7:$H$41,"C")</f>
@@ -28565,27 +28576,27 @@
     <row r="48" spans="1:35">
       <c r="F48" s="72"/>
       <c r="G48" s="6"/>
-      <c r="H48" s="396" t="s">
+      <c r="H48" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="I48" s="397"/>
-      <c r="J48" s="397"/>
-      <c r="K48" s="398"/>
+      <c r="I48" s="389"/>
+      <c r="J48" s="389"/>
+      <c r="K48" s="390"/>
       <c r="L48" s="114">
         <f t="shared" ca="1" si="21"/>
-        <v>0.1388888888888889</v>
+        <v>0.11428571428571428</v>
       </c>
       <c r="M48" s="115">
         <f ca="1">SUM(N48:O48)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N48" s="98">
         <f ca="1">COUNTIFS($I$7:$I$41,"&lt;=21",$U$7:$U$41,"",$K$7:$K$41,"&lt;&gt;X")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O48" s="50">
         <f ca="1">COUNTIFS($I$7:$I$41,"&gt;21",$U$7:$U$41,"",$K$7:$K$41,"&lt;&gt;X")</f>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="P48" s="114">
         <f t="shared" ca="1" si="22"/>
@@ -28613,20 +28624,20 @@
       <c r="AI48" s="11"/>
     </row>
     <row r="49" spans="3:17" ht="16.5" thickBot="1">
-      <c r="C49" s="381" t="s">
+      <c r="C49" s="378" t="s">
         <v>41</v>
       </c>
-      <c r="D49" s="381"/>
-      <c r="E49" s="381"/>
-      <c r="H49" s="399" t="s">
+      <c r="D49" s="378"/>
+      <c r="E49" s="378"/>
+      <c r="H49" s="391" t="s">
         <v>71</v>
       </c>
-      <c r="I49" s="400"/>
-      <c r="J49" s="400"/>
-      <c r="K49" s="401"/>
+      <c r="I49" s="392"/>
+      <c r="J49" s="392"/>
+      <c r="K49" s="393"/>
       <c r="L49" s="113">
         <f t="shared" ca="1" si="21"/>
-        <v>5.5555555555555552E-2</v>
+        <v>5.7142857142857141E-2</v>
       </c>
       <c r="M49" s="97">
         <f>COUNTIFS($K$7:$K$41,"X")</f>
@@ -28668,27 +28679,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="37">
-    <mergeCell ref="P43:Q43"/>
-    <mergeCell ref="X4:Y4"/>
-    <mergeCell ref="Z4:AC4"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="D43:E43"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="D45:E45"/>
-    <mergeCell ref="C49:E49"/>
-    <mergeCell ref="H45:K45"/>
-    <mergeCell ref="H46:K46"/>
-    <mergeCell ref="H43:M43"/>
-    <mergeCell ref="H47:K47"/>
-    <mergeCell ref="H48:K48"/>
-    <mergeCell ref="C46:C47"/>
-    <mergeCell ref="D46:E47"/>
-    <mergeCell ref="D44:E44"/>
     <mergeCell ref="AG5:AG6"/>
     <mergeCell ref="AH5:AH6"/>
     <mergeCell ref="AI5:AI6"/>
@@ -28705,6 +28695,27 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D45:E45"/>
+    <mergeCell ref="C49:E49"/>
+    <mergeCell ref="H45:K45"/>
+    <mergeCell ref="H46:K46"/>
+    <mergeCell ref="H43:M43"/>
+    <mergeCell ref="H47:K47"/>
+    <mergeCell ref="H48:K48"/>
+    <mergeCell ref="C46:C47"/>
+    <mergeCell ref="D46:E47"/>
+    <mergeCell ref="D44:E44"/>
+    <mergeCell ref="P43:Q43"/>
+    <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="Z4:AC4"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="F4:F5"/>
+    <mergeCell ref="G4:G5"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="D43:E43"/>
+    <mergeCell ref="B4:B5"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="A7:AD41 AG7:AI41">
@@ -28869,9 +28880,10 @@
     <hyperlink ref="L38" r:id="rId136" xr:uid="{CEAC5CBD-BC40-4613-AA31-AF1F0C1B782F}"/>
     <hyperlink ref="L39" r:id="rId137" xr:uid="{1260CC6F-397A-4689-AF30-C6ECD668430C}"/>
     <hyperlink ref="N36" r:id="rId138" xr:uid="{A9162BCC-A67F-4960-972B-2EF68F29EB50}"/>
+    <hyperlink ref="N38" r:id="rId139" xr:uid="{DBAA5DC8-908C-4ABF-AC05-BCE08D8BBB73}"/>
   </hyperlinks>
   <pageMargins left="0.25" right="0.17" top="0.5" bottom="0.25" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" scale="29" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId139"/>
+  <pageSetup paperSize="9" scale="29" orientation="landscape" horizontalDpi="300" verticalDpi="300" r:id="rId140"/>
 </worksheet>
 </file>
 
@@ -28916,7 +28928,7 @@
       </c>
       <c r="I1" s="176">
         <f ca="1">TODAY()</f>
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="J1" s="131"/>
       <c r="K1" s="197"/>
@@ -28987,81 +28999,81 @@
       <c r="Z3" s="159"/>
     </row>
     <row r="4" spans="1:26" s="5" customFormat="1" ht="35.1" customHeight="1" thickBot="1">
-      <c r="A4" s="406" t="s">
+      <c r="A4" s="348" t="s">
         <v>0</v>
       </c>
-      <c r="B4" s="406" t="s">
+      <c r="B4" s="348" t="s">
         <v>515</v>
       </c>
-      <c r="C4" s="359" t="s">
+      <c r="C4" s="414" t="s">
         <v>45</v>
       </c>
-      <c r="D4" s="348" t="s">
+      <c r="D4" s="369" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="428" t="s">
+      <c r="E4" s="437" t="s">
         <v>47</v>
       </c>
-      <c r="F4" s="348" t="s">
+      <c r="F4" s="369" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="430" t="s">
+      <c r="G4" s="439" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="352" t="s">
+      <c r="H4" s="366" t="s">
         <v>48</v>
       </c>
-      <c r="I4" s="432" t="s">
+      <c r="I4" s="441" t="s">
         <v>49</v>
       </c>
-      <c r="J4" s="348" t="s">
+      <c r="J4" s="369" t="s">
         <v>78</v>
       </c>
-      <c r="K4" s="352" t="s">
+      <c r="K4" s="366" t="s">
         <v>80</v>
       </c>
-      <c r="L4" s="362" t="s">
+      <c r="L4" s="368" t="s">
         <v>53</v>
       </c>
-      <c r="M4" s="364"/>
-      <c r="N4" s="362" t="s">
+      <c r="M4" s="365"/>
+      <c r="N4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="O4" s="364"/>
-      <c r="P4" s="362" t="s">
+      <c r="O4" s="365"/>
+      <c r="P4" s="368" t="s">
         <v>72</v>
       </c>
-      <c r="Q4" s="364"/>
-      <c r="R4" s="363" t="s">
+      <c r="Q4" s="365"/>
+      <c r="R4" s="364" t="s">
         <v>53</v>
       </c>
-      <c r="S4" s="363"/>
-      <c r="T4" s="364"/>
-      <c r="U4" s="362" t="s">
+      <c r="S4" s="364"/>
+      <c r="T4" s="365"/>
+      <c r="U4" s="368" t="s">
         <v>55</v>
       </c>
-      <c r="V4" s="363"/>
-      <c r="W4" s="363"/>
-      <c r="X4" s="415" t="s">
+      <c r="V4" s="364"/>
+      <c r="W4" s="364"/>
+      <c r="X4" s="371" t="s">
         <v>72</v>
       </c>
-      <c r="Y4" s="416"/>
-      <c r="Z4" s="364" t="s">
+      <c r="Y4" s="372"/>
+      <c r="Z4" s="365" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="72" customHeight="1">
-      <c r="A5" s="407"/>
-      <c r="B5" s="407"/>
-      <c r="C5" s="360"/>
-      <c r="D5" s="354"/>
-      <c r="E5" s="429"/>
-      <c r="F5" s="354"/>
-      <c r="G5" s="431"/>
-      <c r="H5" s="353"/>
-      <c r="I5" s="433"/>
-      <c r="J5" s="354"/>
-      <c r="K5" s="353"/>
+      <c r="A5" s="349"/>
+      <c r="B5" s="349"/>
+      <c r="C5" s="415"/>
+      <c r="D5" s="370"/>
+      <c r="E5" s="438"/>
+      <c r="F5" s="370"/>
+      <c r="G5" s="440"/>
+      <c r="H5" s="367"/>
+      <c r="I5" s="442"/>
+      <c r="J5" s="370"/>
+      <c r="K5" s="367"/>
       <c r="L5" s="79" t="s">
         <v>52</v>
       </c>
@@ -29104,7 +29116,7 @@
       <c r="Y5" s="260" t="s">
         <v>114</v>
       </c>
-      <c r="Z5" s="361"/>
+      <c r="Z5" s="416"/>
     </row>
     <row r="6" spans="1:26" ht="15" customHeight="1" thickBot="1">
       <c r="A6" s="78"/>
@@ -31661,11 +31673,11 @@
       <c r="H39" s="138"/>
       <c r="I39" s="164">
         <f t="shared" ca="1" si="9"/>
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="J39" s="47">
         <f t="shared" ca="1" si="10"/>
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="K39" s="164"/>
       <c r="L39" s="40"/>
@@ -34067,11 +34079,11 @@
       </c>
       <c r="I70" s="164">
         <f t="shared" ref="I70:I78" ca="1" si="14">IF(ISBLANK($V70),_xlfn.DAYS($I$1,$T70),_xlfn.DAYS($V70,$T70))</f>
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J70" s="47">
         <f t="shared" ref="J70:J78" ca="1" si="15">IF(($I70-21)&gt;0,$I70-21,0)</f>
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="K70" s="164"/>
       <c r="L70" s="40"/>
@@ -34097,7 +34109,7 @@
       <c r="X70" s="230"/>
       <c r="Y70" s="19"/>
       <c r="Z70" s="92" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="71" spans="1:26" s="9" customFormat="1" ht="47.25">
@@ -36025,11 +36037,11 @@
       <c r="H97" s="138"/>
       <c r="I97" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="J97" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K97" s="164"/>
       <c r="L97" s="40" t="s">
@@ -37145,11 +37157,11 @@
       <c r="H112" s="138"/>
       <c r="I112" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J112" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K112" s="164" t="s">
         <v>13</v>
@@ -37212,11 +37224,11 @@
       </c>
       <c r="I113" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J113" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K113" s="164"/>
       <c r="L113" s="40" t="s">
@@ -37246,7 +37258,7 @@
       <c r="X113" s="230"/>
       <c r="Y113" s="19"/>
       <c r="Z113" s="92" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="114" spans="1:26" s="9" customFormat="1" ht="63">
@@ -37348,11 +37360,11 @@
       <c r="H115" s="138"/>
       <c r="I115" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="J115" s="47">
         <f t="shared" ca="1" si="25"/>
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="K115" s="164"/>
       <c r="L115" s="40" t="s">
@@ -37518,7 +37530,7 @@
       <c r="X117" s="230"/>
       <c r="Y117" s="19"/>
       <c r="Z117" s="92" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="118" spans="1:26" s="9" customFormat="1" ht="94.5">
@@ -37646,7 +37658,7 @@
       <c r="X119" s="230"/>
       <c r="Y119" s="19"/>
       <c r="Z119" s="92" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="120" spans="1:26" s="9" customFormat="1" ht="110.25">
@@ -37717,7 +37729,7 @@
       <c r="X120" s="230"/>
       <c r="Y120" s="19"/>
       <c r="Z120" s="92" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="121" spans="1:26" s="9" customFormat="1" ht="141.75">
@@ -37788,7 +37800,7 @@
       <c r="X121" s="230"/>
       <c r="Y121" s="19"/>
       <c r="Z121" s="92" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="122" spans="1:26" s="9" customFormat="1" ht="31.5">
@@ -37857,7 +37869,7 @@
       <c r="X122" s="230"/>
       <c r="Y122" s="19"/>
       <c r="Z122" s="92" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="123" spans="1:26" s="9" customFormat="1" ht="47.25">
@@ -37985,7 +37997,7 @@
       <c r="X124" s="230"/>
       <c r="Y124" s="19"/>
       <c r="Z124" s="92" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="125" spans="1:26" s="9" customFormat="1" ht="63">
@@ -38016,7 +38028,7 @@
       <c r="H125" s="138"/>
       <c r="I125" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J125" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -38060,22 +38072,22 @@
         <v>621</v>
       </c>
       <c r="D126" s="25" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E126" s="174">
         <f t="shared" si="23"/>
         <v>46323</v>
       </c>
       <c r="F126" s="31" t="s">
+        <v>1053</v>
+      </c>
+      <c r="G126" s="21" t="s">
         <v>1054</v>
-      </c>
-      <c r="G126" s="21" t="s">
-        <v>1055</v>
       </c>
       <c r="H126" s="138"/>
       <c r="I126" s="164">
         <f t="shared" ca="1" si="24"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J126" s="47">
         <f t="shared" ca="1" si="25"/>
@@ -38167,28 +38179,28 @@
       <c r="C130" s="207" t="s">
         <v>38</v>
       </c>
-      <c r="D130" s="441" t="s">
+      <c r="D130" s="428" t="s">
         <v>39</v>
       </c>
-      <c r="E130" s="442"/>
+      <c r="E130" s="429"/>
       <c r="F130" s="46"/>
       <c r="G130" s="68"/>
-      <c r="H130" s="384" t="s">
+      <c r="H130" s="356" t="s">
         <v>14</v>
       </c>
-      <c r="I130" s="385"/>
-      <c r="J130" s="385"/>
-      <c r="K130" s="385"/>
-      <c r="L130" s="385"/>
-      <c r="M130" s="386"/>
-      <c r="N130" s="382" t="s">
+      <c r="I130" s="357"/>
+      <c r="J130" s="357"/>
+      <c r="K130" s="357"/>
+      <c r="L130" s="357"/>
+      <c r="M130" s="358"/>
+      <c r="N130" s="362" t="s">
         <v>7</v>
       </c>
-      <c r="O130" s="383"/>
-      <c r="P130" s="382" t="s">
+      <c r="O130" s="363"/>
+      <c r="P130" s="362" t="s">
         <v>110</v>
       </c>
-      <c r="Q130" s="383"/>
+      <c r="Q130" s="363"/>
       <c r="R130" s="1"/>
       <c r="S130" s="1"/>
       <c r="T130" s="140"/>
@@ -38201,16 +38213,16 @@
       <c r="C131" s="208" t="s">
         <v>74</v>
       </c>
-      <c r="D131" s="439" t="s">
+      <c r="D131" s="435" t="s">
         <v>77</v>
       </c>
-      <c r="E131" s="440"/>
+      <c r="E131" s="436"/>
       <c r="F131" s="46"/>
       <c r="G131" s="46"/>
-      <c r="H131" s="434" t="s">
+      <c r="H131" s="430" t="s">
         <v>17</v>
       </c>
-      <c r="I131" s="435"/>
+      <c r="I131" s="431"/>
       <c r="J131" s="130"/>
       <c r="K131" s="210"/>
       <c r="L131" s="117">
@@ -38244,21 +38256,21 @@
       <c r="Y131" s="11"/>
     </row>
     <row r="132" spans="3:25">
-      <c r="C132" s="402" t="s">
+      <c r="C132" s="394" t="s">
         <v>6</v>
       </c>
-      <c r="D132" s="439" t="s">
+      <c r="D132" s="435" t="s">
         <v>40</v>
       </c>
-      <c r="E132" s="440"/>
+      <c r="E132" s="436"/>
       <c r="F132" s="69"/>
       <c r="G132" s="6"/>
-      <c r="H132" s="436" t="s">
+      <c r="H132" s="432" t="s">
         <v>69</v>
       </c>
-      <c r="I132" s="437"/>
-      <c r="J132" s="437"/>
-      <c r="K132" s="438"/>
+      <c r="I132" s="433"/>
+      <c r="J132" s="433"/>
+      <c r="K132" s="434"/>
       <c r="L132" s="122">
         <f t="shared" ref="L132:L134" ca="1" si="58">M132/$M$131</f>
         <v>0.83064516129032262</v>
@@ -38292,17 +38304,17 @@
       <c r="Y132" s="11"/>
     </row>
     <row r="133" spans="3:25">
-      <c r="C133" s="402"/>
-      <c r="D133" s="439"/>
-      <c r="E133" s="440"/>
+      <c r="C133" s="394"/>
+      <c r="D133" s="435"/>
+      <c r="E133" s="436"/>
       <c r="F133" s="72"/>
       <c r="G133" s="6"/>
-      <c r="H133" s="396" t="s">
+      <c r="H133" s="388" t="s">
         <v>70</v>
       </c>
-      <c r="I133" s="397"/>
-      <c r="J133" s="397"/>
-      <c r="K133" s="398"/>
+      <c r="I133" s="389"/>
+      <c r="J133" s="389"/>
+      <c r="K133" s="390"/>
       <c r="L133" s="124">
         <f t="shared" ca="1" si="58"/>
         <v>5.6451612903225805E-2</v>
@@ -38338,19 +38350,19 @@
       <c r="Y133" s="11"/>
     </row>
     <row r="134" spans="3:25" ht="16.5" thickBot="1">
-      <c r="C134" s="402" t="s">
+      <c r="C134" s="394" t="s">
         <v>75</v>
       </c>
-      <c r="D134" s="408" t="s">
+      <c r="D134" s="350" t="s">
         <v>76</v>
       </c>
-      <c r="E134" s="409"/>
-      <c r="H134" s="399" t="s">
+      <c r="E134" s="351"/>
+      <c r="H134" s="391" t="s">
         <v>71</v>
       </c>
-      <c r="I134" s="400"/>
-      <c r="J134" s="400"/>
-      <c r="K134" s="401"/>
+      <c r="I134" s="392"/>
+      <c r="J134" s="392"/>
+      <c r="K134" s="393"/>
       <c r="L134" s="126">
         <f t="shared" ca="1" si="58"/>
         <v>0.11290322580645161</v>
@@ -38365,16 +38377,16 @@
       <c r="Q134" s="224"/>
     </row>
     <row r="135" spans="3:25" ht="16.5" thickBot="1">
-      <c r="C135" s="403"/>
-      <c r="D135" s="410"/>
-      <c r="E135" s="411"/>
+      <c r="C135" s="395"/>
+      <c r="D135" s="352"/>
+      <c r="E135" s="353"/>
     </row>
     <row r="137" spans="3:25">
-      <c r="C137" s="381" t="s">
+      <c r="C137" s="378" t="s">
         <v>41</v>
       </c>
-      <c r="D137" s="381"/>
-      <c r="E137" s="381"/>
+      <c r="D137" s="378"/>
+      <c r="E137" s="378"/>
     </row>
     <row r="138" spans="3:25">
       <c r="C138" s="169" t="s">
@@ -38407,22 +38419,6 @@
     </sortState>
   </autoFilter>
   <mergeCells count="32">
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="P130:Q130"/>
-    <mergeCell ref="J4:J5"/>
-    <mergeCell ref="D130:E130"/>
-    <mergeCell ref="H130:M130"/>
-    <mergeCell ref="N130:O130"/>
-    <mergeCell ref="H131:I131"/>
-    <mergeCell ref="C137:E137"/>
-    <mergeCell ref="H132:K132"/>
-    <mergeCell ref="H133:K133"/>
-    <mergeCell ref="H134:K134"/>
-    <mergeCell ref="D131:E131"/>
-    <mergeCell ref="C132:C133"/>
-    <mergeCell ref="D132:E133"/>
-    <mergeCell ref="C134:C135"/>
-    <mergeCell ref="D134:E135"/>
     <mergeCell ref="Z4:Z5"/>
     <mergeCell ref="A4:A5"/>
     <mergeCell ref="D4:D5"/>
@@ -38439,6 +38435,22 @@
     <mergeCell ref="K4:K5"/>
     <mergeCell ref="P4:Q4"/>
     <mergeCell ref="X4:Y4"/>
+    <mergeCell ref="H131:I131"/>
+    <mergeCell ref="C137:E137"/>
+    <mergeCell ref="H132:K132"/>
+    <mergeCell ref="H133:K133"/>
+    <mergeCell ref="H134:K134"/>
+    <mergeCell ref="D131:E131"/>
+    <mergeCell ref="C132:C133"/>
+    <mergeCell ref="D132:E133"/>
+    <mergeCell ref="C134:C135"/>
+    <mergeCell ref="D134:E135"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="P130:Q130"/>
+    <mergeCell ref="J4:J5"/>
+    <mergeCell ref="D130:E130"/>
+    <mergeCell ref="H130:M130"/>
+    <mergeCell ref="N130:O130"/>
   </mergeCells>
   <phoneticPr fontId="71"/>
   <conditionalFormatting sqref="A7:Z128">
@@ -38941,7 +38953,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75733AF3-96C4-423A-BD99-1E08B3C66916}">
-  <dimension ref="A1:Y25"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="13" customWidth="1"/>
@@ -39020,19 +39032,19 @@
       <c r="S3" s="281"/>
     </row>
     <row r="4" spans="1:25" ht="36" customHeight="1" thickBot="1">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="408" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="352" t="s">
+      <c r="B4" s="366" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="352" t="s">
+      <c r="C4" s="366" t="s">
         <v>95</v>
       </c>
-      <c r="D4" s="352" t="s">
+      <c r="D4" s="366" t="s">
         <v>46</v>
       </c>
-      <c r="E4" s="348" t="s">
+      <c r="E4" s="369" t="s">
         <v>4</v>
       </c>
       <c r="F4" s="449" t="s">
@@ -39061,12 +39073,12 @@
       <c r="S4" s="448"/>
     </row>
     <row r="5" spans="1:25" ht="78.75">
-      <c r="A5" s="351"/>
-      <c r="B5" s="353"/>
-      <c r="C5" s="353"/>
-      <c r="D5" s="353"/>
-      <c r="E5" s="354"/>
-      <c r="F5" s="356"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="367"/>
+      <c r="C5" s="367"/>
+      <c r="D5" s="367"/>
+      <c r="E5" s="370"/>
+      <c r="F5" s="411"/>
       <c r="G5" s="283" t="s">
         <v>56</v>
       </c>
@@ -39130,131 +39142,131 @@
     </row>
     <row r="7" spans="1:25" ht="45">
       <c r="A7" s="13" cm="1">
-        <f t="array" ref="A7:A25">IF(_xlfn.ANCHORARRAY(D7)="","",_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(D7))))</f>
+        <f t="array" ref="A7:A24">IF(_xlfn.ANCHORARRAY(D7)="","",_xlfn.SEQUENCE(ROWS(_xlfn.ANCHORARRAY(D7))))</f>
         <v>1</v>
       </c>
       <c r="B7" s="302" t="str" cm="1">
-        <f t="array" ref="B7:B25">_xlfn.LET(
+        <f t="array" ref="B7:B24">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$C:$C,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>FAS</v>
       </c>
       <c r="C7" s="13" t="str" cm="1">
-        <f t="array" ref="C7:C25">_xlfn.LET(
+        <f t="array" ref="C7:C24">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$D:$D,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>MAS</v>
       </c>
       <c r="D7" s="282" t="str" cm="1">
-        <f t="array" ref="D7:D25">_xlfn._xlws.FILTER(RFA!$E$5:$E$4572, RFA!$AI$5:$AI$4572="YES","")</f>
+        <f t="array" ref="D7:D24">_xlfn._xlws.FILTER(RFA!$E$5:$E$4572, RFA!$AI$5:$AI$4572="YES","")</f>
         <v>LTIA-5.10-VIETUR-70000-RFA-MAS-0088A</v>
       </c>
       <c r="E7" s="303" t="str" cm="1">
-        <f t="array" ref="E7:E25">_xlfn.LET(
+        <f t="array" ref="E7:E24">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$G:$G,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>Request for approval material cable fire resistant shield for fire alarm system (Belden)</v>
       </c>
       <c r="F7" s="303" t="str" cm="1">
-        <f t="array" ref="F7:F25">_xlfn.LET(
+        <f t="array" ref="F7:F24">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$H:$H,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>Đề nghị phê duyệt vật liệu cáp chống cháy cho hệ thống báo cháy (Belden)</v>
       </c>
       <c r="G7" s="270" cm="1">
-        <f t="array" ref="G7:G25">_xlfn.LET(
+        <f t="array" ref="G7:G24">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$S:$S,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45426</v>
       </c>
       <c r="H7" s="270" cm="1">
-        <f t="array" ref="H7:H25">_xlfn.LET(
+        <f t="array" ref="H7:H24">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$T:$T,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45426</v>
       </c>
       <c r="I7" s="264" cm="1">
-        <f t="array" ref="I7:I25">_xlfn.LET(
+        <f t="array" ref="I7:I24">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$U:$U,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45426</v>
       </c>
       <c r="J7" s="264" t="str" cm="1">
-        <f t="array" ref="J7:J25">_xlfn.LET(
+        <f t="array" ref="J7:J24">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$I:$I,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>C</v>
       </c>
       <c r="K7" s="270" cm="1">
-        <f t="array" ref="K7:K25">_xlfn.LET(
+        <f t="array" ref="K7:K24">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$V:$V,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45454</v>
       </c>
       <c r="L7" s="264" cm="1">
-        <f t="array" ref="L7:L25">_xlfn.LET(
+        <f t="array" ref="L7:L24">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$W:$W,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45455</v>
       </c>
       <c r="M7" s="264" t="str" cm="1">
-        <f t="array" ref="M7:M25">_xlfn.LET(
+        <f t="array" ref="M7:M24">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$R:$R,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>C</v>
       </c>
       <c r="N7" s="270" cm="1">
-        <f t="array" ref="N7:N25">_xlfn.LET(
+        <f t="array" ref="N7:N24">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$Y:$Y,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45456</v>
       </c>
       <c r="O7" s="264" cm="1">
-        <f t="array" ref="O7:O25">_xlfn.LET(
+        <f t="array" ref="O7:O24">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$Z:$Z,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45456</v>
       </c>
       <c r="P7" s="264" cm="1">
-        <f t="array" ref="P7:P25">_xlfn.LET(
+        <f t="array" ref="P7:P24">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AA:$AA,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>45463</v>
       </c>
       <c r="Q7" s="270" t="str" cm="1">
-        <f t="array" ref="Q7:Q25">_xlfn.LET(
+        <f t="array" ref="Q7:Q24">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AB:$AB,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v/>
       </c>
       <c r="R7" s="13" t="str" cm="1">
-        <f t="array" aca="1" ref="R7:R25" ca="1">_xlfn.LET(
+        <f t="array" aca="1" ref="R7:R24" ca="1">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AC:$AC,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
         <v>Not submit yet</v>
       </c>
       <c r="S7" s="279" cm="1">
-        <f t="array" aca="1" ref="S7:S25" ca="1">_xlfn.LET(
+        <f t="array" aca="1" ref="S7:S24" ca="1">_xlfn.LET(
 _xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(D7),RFA!$E:$E,RFA!$AD:$AD,""),
 IF(_xlpm.x=0,"",_xlpm.x)
 )</f>
-        <v>840</v>
+        <v>841</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="45">
@@ -39315,7 +39327,7 @@
       </c>
       <c r="S8" s="279">
         <f ca="1"/>
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="Y8" t="s">
         <v>125</v>
@@ -39380,7 +39392,7 @@
       </c>
       <c r="S9" s="279">
         <f ca="1"/>
-        <v>503</v>
+        <v>504</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="45">
@@ -39441,7 +39453,7 @@
       </c>
       <c r="S10" s="279">
         <f ca="1"/>
-        <v>384</v>
+        <v>385</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="75">
@@ -39502,7 +39514,7 @@
       </c>
       <c r="S11" s="279">
         <f ca="1"/>
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="45">
@@ -39563,7 +39575,7 @@
       </c>
       <c r="S12" s="279">
         <f ca="1"/>
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="45">
@@ -39624,7 +39636,7 @@
       </c>
       <c r="S13" s="279">
         <f ca="1"/>
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="45">
@@ -39685,7 +39697,7 @@
       </c>
       <c r="S14" s="279">
         <f ca="1"/>
-        <v>133</v>
+        <v>134</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="60">
@@ -40241,39 +40253,39 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:19" ht="30">
+    <row r="24" spans="1:19" ht="105">
       <c r="A24" s="13">
         <v>18</v>
       </c>
       <c r="B24" s="302" t="str">
-        <v>SCN</v>
+        <v>FAS</v>
       </c>
       <c r="C24" s="13" t="str">
-        <v>MAS</v>
+        <v>OTH</v>
       </c>
       <c r="D24" s="282" t="str">
-        <v xml:space="preserve">LTIA-5.10-VIETUR-70000-RFA-MAS-0821 </v>
+        <v>LTIA-5.10-VIETUR-70000-RFA-OTH-0733A</v>
       </c>
       <c r="E24" s="303" t="str">
-        <v>Request for approval of additional ICT cable – ELV System</v>
+        <v>Request for approval Pre-completion inspection, testing, and commissioning: + Section 70000 – ICT works/ Subsection 72000 – Extra-low Voltage System (ELV) and Communication/ Division 72160 – Fire Alarm System (FAS)</v>
       </c>
       <c r="F24" s="303" t="str">
-        <v>Đề nghị phê duyệt bổ sung vật tư cáp điện nhẹ - Hệ thống điện nhẹ</v>
+        <v>Đề nghị phê duyệt Kiểm tra trước khi hoàn thành, thử nghiệm và vận hành: + Phần 70000 – Công tác ICT/ Mục 72000 – Hệ thống điện nhẹ (ELV) &amp; Truyền thông/ Tiểu mục 72160 – Hệ thống báo cháy (FAS)</v>
       </c>
       <c r="G24" s="270">
-        <v>46280</v>
+        <v>46289</v>
       </c>
       <c r="H24" s="270">
-        <v>46280</v>
+        <v>46289</v>
       </c>
       <c r="I24" s="264">
-        <v>46280</v>
+        <v>46289</v>
       </c>
       <c r="J24" s="264" t="str">
         <v>C</v>
       </c>
       <c r="K24" s="270">
-        <v>46290</v>
+        <v>46297</v>
       </c>
       <c r="L24" s="264">
         <v>46300</v>
@@ -40298,67 +40310,6 @@
         <v/>
       </c>
       <c r="S24" s="279" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:19" ht="105">
-      <c r="A25" s="13">
-        <v>19</v>
-      </c>
-      <c r="B25" s="302" t="str">
-        <v>FAS</v>
-      </c>
-      <c r="C25" s="13" t="str">
-        <v>OTH</v>
-      </c>
-      <c r="D25" s="282" t="str">
-        <v>LTIA-5.10-VIETUR-70000-RFA-OTH-0733A</v>
-      </c>
-      <c r="E25" s="303" t="str">
-        <v>Request for approval Pre-completion inspection, testing, and commissioning: + Section 70000 – ICT works/ Subsection 72000 – Extra-low Voltage System (ELV) and Communication/ Division 72160 – Fire Alarm System (FAS)</v>
-      </c>
-      <c r="F25" s="303" t="str">
-        <v>Đề nghị phê duyệt Kiểm tra trước khi hoàn thành, thử nghiệm và vận hành: + Phần 70000 – Công tác ICT/ Mục 72000 – Hệ thống điện nhẹ (ELV) &amp; Truyền thông/ Tiểu mục 72160 – Hệ thống báo cháy (FAS)</v>
-      </c>
-      <c r="G25" s="270">
-        <v>46289</v>
-      </c>
-      <c r="H25" s="270">
-        <v>46289</v>
-      </c>
-      <c r="I25" s="264">
-        <v>46289</v>
-      </c>
-      <c r="J25" s="264" t="str">
-        <v>C</v>
-      </c>
-      <c r="K25" s="270">
-        <v>46297</v>
-      </c>
-      <c r="L25" s="264">
-        <v>46300</v>
-      </c>
-      <c r="M25" s="264" t="str">
-        <v/>
-      </c>
-      <c r="N25" s="270" t="str">
-        <v/>
-      </c>
-      <c r="O25" s="264" t="str">
-        <v/>
-      </c>
-      <c r="P25" s="264">
-        <v>46307</v>
-      </c>
-      <c r="Q25" s="270" t="str">
-        <v/>
-      </c>
-      <c r="R25" s="13" t="str">
-        <f ca="1"/>
-        <v/>
-      </c>
-      <c r="S25" s="279" t="str">
         <f ca="1"/>
         <v/>
       </c>
@@ -40460,16 +40411,16 @@
       <c r="R3" s="281"/>
     </row>
     <row r="4" spans="1:18" ht="16.5" thickBot="1">
-      <c r="A4" s="350" t="s">
+      <c r="A4" s="408" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="352" t="s">
+      <c r="B4" s="366" t="s">
         <v>45</v>
       </c>
-      <c r="C4" s="352" t="s">
+      <c r="C4" s="366" t="s">
         <v>46</v>
       </c>
-      <c r="D4" s="363" t="s">
+      <c r="D4" s="364" t="s">
         <v>4</v>
       </c>
       <c r="E4" s="449" t="s">
@@ -40498,11 +40449,11 @@
       <c r="R4" s="448"/>
     </row>
     <row r="5" spans="1:18" ht="78.75">
-      <c r="A5" s="351"/>
-      <c r="B5" s="353"/>
-      <c r="C5" s="353"/>
-      <c r="D5" s="431"/>
-      <c r="E5" s="354"/>
+      <c r="A5" s="409"/>
+      <c r="B5" s="367"/>
+      <c r="C5" s="367"/>
+      <c r="D5" s="440"/>
+      <c r="E5" s="370"/>
       <c r="F5" s="283" t="s">
         <v>56</v>
       </c>
@@ -40638,7 +40589,7 @@
       </c>
       <c r="R7" s="279" cm="1">
         <f t="array" aca="1" ref="R7:R18" ca="1">_xlfn.LET(_xlpm.x,_xlfn.XLOOKUP(_xlfn.ANCHORARRAY(C7),'RFA-SDS'!$D:$D,'RFA-SDS'!$AC:$AC,""),IF(_xlpm.x=0,"",_xlpm.x))</f>
-        <v>540</v>
+        <v>541</v>
       </c>
     </row>
     <row r="8" spans="1:18" ht="30">
@@ -40696,7 +40647,7 @@
       </c>
       <c r="R8" s="279">
         <f ca="1"/>
-        <v>450</v>
+        <v>451</v>
       </c>
     </row>
     <row r="9" spans="1:18" ht="45">
@@ -40754,7 +40705,7 @@
       </c>
       <c r="R9" s="279">
         <f ca="1"/>
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="10" spans="1:18" ht="105">
@@ -40813,7 +40764,7 @@
       </c>
       <c r="R10" s="279">
         <f ca="1"/>
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11" spans="1:18" ht="45">
@@ -40871,7 +40822,7 @@
       </c>
       <c r="R11" s="279">
         <f ca="1"/>
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="12" spans="1:18" ht="45">
@@ -40930,7 +40881,7 @@
       </c>
       <c r="R12" s="279">
         <f ca="1"/>
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="13" spans="1:18" ht="75">
@@ -40988,7 +40939,7 @@
       </c>
       <c r="R13" s="279">
         <f ca="1"/>
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="14" spans="1:18" ht="60">
@@ -41046,7 +40997,7 @@
       </c>
       <c r="R14" s="279">
         <f ca="1"/>
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="15" spans="1:18" ht="45">
@@ -41104,7 +41055,7 @@
       </c>
       <c r="R15" s="279">
         <f ca="1"/>
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="16" spans="1:18" ht="45">
@@ -41162,7 +41113,7 @@
       </c>
       <c r="R16" s="279">
         <f ca="1"/>
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="17" spans="1:18" ht="60">
@@ -41278,7 +41229,7 @@
       </c>
       <c r="R18" s="279">
         <f ca="1"/>
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
   </sheetData>
@@ -41336,19 +41287,19 @@
     <row r="3" spans="1:4" ht="15.75">
       <c r="A3" s="319">
         <f ca="1">MAX('Need ReSub (RFA)'!S7:S76)</f>
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="B3" s="319">
         <f ca="1">AVERAGEIF('Need ReSub (RFA)'!S7:S76,"&lt;&gt;0")</f>
-        <v>448.25</v>
+        <v>449.25</v>
       </c>
       <c r="C3" s="319">
         <f ca="1">MAX(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7))</f>
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D3" s="319">
         <f ca="1">AVERAGEIF(_xlfn.ANCHORARRAY('Need ReSub (RFA-SDS)'!R7),"&lt;&gt;0")</f>
-        <v>332.25</v>
+        <v>333.16666666666669</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -41357,10 +41308,10 @@
 Furthermore, the RFA (SDS) is as follows:
 Avarage :  " &amp; ROUND($D$3,0) &amp; " days
 Maimum :  " &amp; ROUND($C$3,0) &amp; " days"</f>
-        <v>In the RFA process, the average number of days elapsed since responding to an unapproved RFA was 448 days, with a maximum of 840 days, indicating that delays in the RFA approval process are contributing to delays in construction work.
+        <v>In the RFA process, the average number of days elapsed since responding to an unapproved RFA was 449 days, with a maximum of 841 days, indicating that delays in the RFA approval process are contributing to delays in construction work.
 Furthermore, the RFA (SDS) is as follows:
-Avarage :  332 days
-Maimum :  540 days</v>
+Avarage :  333 days
+Maimum :  541 days</v>
       </c>
       <c r="B5" s="452"/>
     </row>
